--- a/2016ElectionPolls.xlsx
+++ b/2016ElectionPolls.xlsx
@@ -1097,14 +1097,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0%"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
-    <numFmt numFmtId="167" formatCode="d\-mmm\-yy"/>
-    <numFmt numFmtId="168" formatCode="0.00%"/>
+    <numFmt numFmtId="167" formatCode="@"/>
+    <numFmt numFmtId="168" formatCode="d\-mmm\-yy"/>
+    <numFmt numFmtId="169" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1147,6 +1148,14 @@
       <sz val="11"/>
       <color rgb="FF202122"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -1240,7 +1249,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1289,19 +1298,27 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1321,7 +1338,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1341,7 +1358,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1349,8 +1370,12 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1603,7 +1628,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L257"/>
+  <dimension ref="A1:S256"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.78"/>
@@ -1638,6 +1663,7 @@
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
       <c r="L1" s="8"/>
+      <c r="Q1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -1662,22 +1688,29 @@
         <v>4135</v>
       </c>
       <c r="H2" s="6"/>
-      <c r="L2" s="8"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="n">
+      <c r="A3" s="15" t="n">
         <v>42551</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="16" t="n">
         <v>0.428</v>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="16" t="n">
         <v>0.346</v>
       </c>
-      <c r="E3" s="13" t="n">
+      <c r="E3" s="16" t="n">
         <v>0.107</v>
       </c>
       <c r="F3" s="10" t="n">
@@ -1686,10 +1719,15 @@
       <c r="G3" s="11" t="n">
         <v>2084</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="8"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
@@ -1698,13 +1736,13 @@
       <c r="B4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="16" t="n">
         <v>0.425</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="16" t="n">
         <v>0.345</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="16" t="n">
         <v>0.115</v>
       </c>
       <c r="F4" s="10" t="n">
@@ -1713,10 +1751,15 @@
       <c r="G4" s="11" t="n">
         <v>1212</v>
       </c>
-      <c r="H4" s="16"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="8"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -1740,10 +1783,15 @@
       <c r="G5" s="11" t="n">
         <v>1768</v>
       </c>
-      <c r="H5" s="14"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="8"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -1767,10 +1815,15 @@
       <c r="G6" s="11" t="n">
         <v>1377</v>
       </c>
-      <c r="H6" s="16"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="8"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -1794,10 +1847,15 @@
       <c r="G7" s="11" t="n">
         <v>1773</v>
       </c>
-      <c r="H7" s="17"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="8"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
@@ -1821,43 +1879,53 @@
       <c r="G8" s="11" t="n">
         <v>1713</v>
       </c>
-      <c r="H8" s="17"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="8"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="n">
+      <c r="A9" s="15" t="n">
         <v>42544</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="16" t="n">
         <v>0.423</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="16" t="n">
         <v>0.337</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="16" t="n">
         <v>0.105</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="16" t="n">
         <v>0.133</v>
       </c>
       <c r="G9" s="11" t="n">
         <v>2349</v>
       </c>
-      <c r="H9" s="16"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="8"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="20" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="10" t="n">
@@ -1872,13 +1940,18 @@
       <c r="F10" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="21" t="n">
         <v>1700</v>
       </c>
-      <c r="H10" s="16"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="8"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
@@ -1902,10 +1975,15 @@
       <c r="G11" s="11" t="n">
         <v>1013</v>
       </c>
-      <c r="H11" s="17"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="8"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
@@ -1929,37 +2007,47 @@
       <c r="G12" s="11" t="n">
         <v>1805</v>
       </c>
-      <c r="H12" s="17"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="8"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="n">
+      <c r="A13" s="15" t="n">
         <v>42537</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="16" t="n">
         <v>0.435</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="16" t="n">
         <v>0.336</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="16" t="n">
         <v>0.091</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="16" t="n">
         <v>0.137</v>
       </c>
       <c r="G13" s="11" t="n">
         <v>2576</v>
       </c>
-      <c r="H13" s="17"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="8"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
@@ -1983,10 +2071,15 @@
       <c r="G14" s="11" t="n">
         <v>1437</v>
       </c>
-      <c r="H14" s="16"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="8"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
@@ -2010,37 +2103,47 @@
       <c r="G15" s="11" t="n">
         <v>1784</v>
       </c>
-      <c r="H15" s="17"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="8"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="15" t="n">
         <v>42530</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="16" t="n">
         <v>0.427</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="16" t="n">
         <v>0.332</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="16" t="n">
         <v>0.099</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="16" t="n">
         <v>0.143</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>2175</v>
       </c>
-      <c r="H16" s="17"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="8"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="R16" s="13"/>
+      <c r="S16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
@@ -2064,10 +2167,15 @@
       <c r="G17" s="11" t="n">
         <v>1772</v>
       </c>
-      <c r="H17" s="17"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="8"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
@@ -2091,37 +2199,47 @@
       <c r="G18" s="11" t="n">
         <v>1867</v>
       </c>
-      <c r="H18" s="17"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="8"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="n">
+      <c r="A19" s="15" t="n">
         <v>42523</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="16" t="n">
         <v>0.415</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="16" t="n">
         <v>0.349</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="16" t="n">
         <v>0.101</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="16" t="n">
         <v>0.135</v>
       </c>
       <c r="G19" s="11" t="n">
         <v>2414</v>
       </c>
-      <c r="H19" s="17"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="8"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
@@ -2145,10 +2263,15 @@
       <c r="G20" s="11" t="n">
         <v>1359</v>
       </c>
-      <c r="H20" s="17"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="8"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
@@ -2172,10 +2295,15 @@
       <c r="G21" s="11" t="n">
         <v>1767</v>
       </c>
-      <c r="H21" s="17"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="8"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
@@ -2184,10 +2312,10 @@
       <c r="B22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C22" s="16" t="n">
         <v>0.375</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="16" t="n">
         <v>0.325</v>
       </c>
       <c r="E22" s="10" t="n">
@@ -2199,37 +2327,47 @@
       <c r="G22" s="11" t="n">
         <v>3099</v>
       </c>
-      <c r="H22" s="16"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="8"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="15" t="n">
         <v>42516</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="16" t="n">
         <v>0.411</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="16" t="n">
         <v>0.365</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="16" t="n">
         <v>0.096</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F23" s="16" t="n">
         <v>0.128</v>
       </c>
       <c r="G23" s="11" t="n">
         <v>2700</v>
       </c>
-      <c r="H23" s="17"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="8"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
@@ -2253,10 +2391,15 @@
       <c r="G24" s="11" t="n">
         <v>1794</v>
       </c>
-      <c r="H24" s="17"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="8"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
@@ -2277,40 +2420,50 @@
       <c r="F25" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="G25" s="19" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H25" s="17"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="8"/>
+      <c r="G25" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H25" s="19"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="n">
+      <c r="A26" s="15" t="n">
         <v>42509</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C26" s="16" t="n">
         <v>0.426</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="16" t="n">
         <v>0.366</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="16" t="n">
         <v>0.099</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F26" s="16" t="n">
         <v>0.109</v>
       </c>
       <c r="G26" s="11" t="n">
         <v>2407</v>
       </c>
-      <c r="H26" s="17"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="8"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="R26" s="13"/>
+      <c r="S26" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
@@ -2334,10 +2487,15 @@
       <c r="G27" s="11" t="n">
         <v>1497</v>
       </c>
-      <c r="H27" s="17"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="8"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="R27" s="13"/>
+      <c r="S27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
@@ -2346,13 +2504,13 @@
       <c r="B28" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="13" t="n">
+      <c r="C28" s="16" t="n">
         <v>0.365</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>0.33</v>
       </c>
-      <c r="E28" s="13" t="n">
+      <c r="E28" s="16" t="n">
         <v>0.155</v>
       </c>
       <c r="F28" s="10" t="n">
@@ -2361,10 +2519,15 @@
       <c r="G28" s="11" t="n">
         <v>2318</v>
       </c>
-      <c r="H28" s="16"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="8"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="R28" s="13"/>
+      <c r="S28" s="13"/>
     </row>
     <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
@@ -2388,10 +2551,15 @@
       <c r="G29" s="11" t="n">
         <v>1784</v>
       </c>
-      <c r="H29" s="20"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="8"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="R29" s="13"/>
+      <c r="S29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
@@ -2415,10 +2583,15 @@
       <c r="G30" s="11" t="n">
         <v>1841</v>
       </c>
-      <c r="H30" s="17"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="8"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="R30" s="13"/>
+      <c r="S30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
@@ -2442,10 +2615,15 @@
       <c r="G31" s="11" t="n">
         <v>1754</v>
       </c>
-      <c r="H31" s="17"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="8"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="R31" s="13"/>
+      <c r="S31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
@@ -2466,13 +2644,18 @@
       <c r="F32" s="10" t="n">
         <v>0.11</v>
       </c>
-      <c r="G32" s="19" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H32" s="17"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="8"/>
+      <c r="G32" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H32" s="19"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+      <c r="R32" s="13"/>
+      <c r="S32" s="13"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
@@ -2496,10 +2679,15 @@
       <c r="G33" s="11" t="n">
         <v>1410</v>
       </c>
-      <c r="H33" s="17"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="8"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="R33" s="13"/>
+      <c r="S33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
@@ -2523,37 +2711,47 @@
       <c r="G34" s="11" t="n">
         <v>1739</v>
       </c>
-      <c r="H34" s="16"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="8"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="R34" s="13"/>
+      <c r="S34" s="13"/>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12" t="n">
+      <c r="A35" s="15" t="n">
         <v>42495</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="13" t="n">
+      <c r="C35" s="16" t="n">
         <v>0.432</v>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="16" t="n">
         <v>0.351</v>
       </c>
-      <c r="E35" s="13" t="n">
+      <c r="E35" s="16" t="n">
         <v>0.095</v>
       </c>
-      <c r="F35" s="13" t="n">
+      <c r="F35" s="16" t="n">
         <v>0.122</v>
       </c>
       <c r="G35" s="11" t="n">
         <v>2450</v>
       </c>
-      <c r="H35" s="17"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="8"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="R35" s="13"/>
+      <c r="S35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
@@ -2577,10 +2775,15 @@
       <c r="G36" s="11" t="n">
         <v>1753</v>
       </c>
-      <c r="H36" s="17"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="8"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="R36" s="13"/>
+      <c r="S36" s="13"/>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
@@ -2592,10 +2795,10 @@
       <c r="C37" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="16" t="n">
         <v>0.325</v>
       </c>
-      <c r="E37" s="13" t="n">
+      <c r="E37" s="16" t="n">
         <v>0.135</v>
       </c>
       <c r="F37" s="10" t="n">
@@ -2604,10 +2807,15 @@
       <c r="G37" s="11" t="n">
         <v>2951</v>
       </c>
-      <c r="H37" s="17"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="8"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="R37" s="13"/>
+      <c r="S37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
@@ -2631,10 +2839,15 @@
       <c r="G38" s="11" t="n">
         <v>1740</v>
       </c>
-      <c r="H38" s="17"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="8"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
+      <c r="R38" s="13"/>
+      <c r="S38" s="13"/>
     </row>
     <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
@@ -2655,13 +2868,18 @@
       <c r="F39" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="G39" s="19" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H39" s="17"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="8"/>
+      <c r="G39" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H39" s="19"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="14"/>
+      <c r="L39" s="14"/>
+      <c r="M39" s="14"/>
+      <c r="N39" s="14"/>
+      <c r="R39" s="13"/>
+      <c r="S39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
@@ -2685,10 +2903,15 @@
       <c r="G40" s="11" t="n">
         <v>1753</v>
       </c>
-      <c r="H40" s="17"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="8"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="14"/>
+      <c r="R40" s="13"/>
+      <c r="S40" s="13"/>
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
@@ -2697,7 +2920,7 @@
       <c r="B41" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C41" s="13" t="n">
+      <c r="C41" s="16" t="n">
         <v>0.405</v>
       </c>
       <c r="D41" s="10" t="n">
@@ -2706,16 +2929,21 @@
       <c r="E41" s="10" t="n">
         <v>0.14</v>
       </c>
-      <c r="F41" s="13" t="n">
+      <c r="F41" s="16" t="n">
         <v>0.135</v>
       </c>
       <c r="G41" s="11" t="n">
         <v>3083</v>
       </c>
-      <c r="H41" s="17"/>
-      <c r="J41" s="15"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="8"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14"/>
+      <c r="N41" s="14"/>
+      <c r="R41" s="13"/>
+      <c r="S41" s="13"/>
     </row>
     <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
@@ -2739,37 +2967,47 @@
       <c r="G42" s="11" t="n">
         <v>1402</v>
       </c>
-      <c r="H42" s="17"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="8"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="13"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="14"/>
+      <c r="R42" s="13"/>
+      <c r="S42" s="13"/>
     </row>
     <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="12" t="n">
+      <c r="A43" s="15" t="n">
         <v>42474</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C43" s="13" t="n">
+      <c r="C43" s="16" t="n">
         <v>0.435</v>
       </c>
-      <c r="D43" s="13" t="n">
+      <c r="D43" s="16" t="n">
         <v>0.358</v>
       </c>
-      <c r="E43" s="13" t="n">
+      <c r="E43" s="16" t="n">
         <v>0.098</v>
       </c>
-      <c r="F43" s="13" t="n">
+      <c r="F43" s="16" t="n">
         <v>0.109</v>
       </c>
       <c r="G43" s="11" t="n">
         <v>2415</v>
       </c>
-      <c r="H43" s="17"/>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="8"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="13"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="14"/>
+      <c r="N43" s="14"/>
+      <c r="R43" s="13"/>
+      <c r="S43" s="13"/>
     </row>
     <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
@@ -2793,10 +3031,15 @@
       <c r="G44" s="11" t="n">
         <v>1792</v>
       </c>
-      <c r="H44" s="17"/>
-      <c r="J44" s="15"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="8"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="14"/>
+      <c r="L44" s="14"/>
+      <c r="M44" s="14"/>
+      <c r="N44" s="14"/>
+      <c r="R44" s="13"/>
+      <c r="S44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
@@ -2817,13 +3060,18 @@
       <c r="F45" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="G45" s="19" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H45" s="17"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="8"/>
+      <c r="G45" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H45" s="19"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="13"/>
+      <c r="K45" s="14"/>
+      <c r="L45" s="14"/>
+      <c r="M45" s="14"/>
+      <c r="N45" s="14"/>
+      <c r="R45" s="13"/>
+      <c r="S45" s="13"/>
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
@@ -2847,37 +3095,47 @@
       <c r="G46" s="11" t="n">
         <v>3174</v>
       </c>
-      <c r="H46" s="17"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="8"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="14"/>
+      <c r="L46" s="14"/>
+      <c r="M46" s="14"/>
+      <c r="N46" s="14"/>
+      <c r="R46" s="13"/>
+      <c r="S46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="12" t="n">
+      <c r="A47" s="15" t="n">
         <v>42450</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C47" s="13" t="n">
+      <c r="C47" s="16" t="n">
         <v>0.466</v>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D47" s="16" t="n">
         <v>0.344</v>
       </c>
-      <c r="E47" s="13" t="n">
+      <c r="E47" s="16" t="n">
         <v>0.105</v>
       </c>
-      <c r="F47" s="13" t="n">
+      <c r="F47" s="16" t="n">
         <v>0.086</v>
       </c>
       <c r="G47" s="11" t="n">
         <v>3274</v>
       </c>
-      <c r="H47" s="14"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="8"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="14"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="14"/>
+      <c r="N47" s="14"/>
+      <c r="R47" s="13"/>
+      <c r="S47" s="13"/>
     </row>
     <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
@@ -2898,13 +3156,18 @@
       <c r="F48" s="10" t="n">
         <v>0.11</v>
       </c>
-      <c r="G48" s="19" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H48" s="16"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="8"/>
+      <c r="G48" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H48" s="18"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="14"/>
+      <c r="L48" s="14"/>
+      <c r="M48" s="14"/>
+      <c r="N48" s="14"/>
+      <c r="R48" s="13"/>
+      <c r="S48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
@@ -2928,10 +3191,15 @@
       <c r="G49" s="11" t="n">
         <v>1790</v>
       </c>
-      <c r="H49" s="16"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="15"/>
-      <c r="L49" s="8"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="13"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="14"/>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
+      <c r="R49" s="13"/>
+      <c r="S49" s="13"/>
     </row>
     <row r="50" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
@@ -2955,37 +3223,45 @@
       <c r="G50" s="11" t="n">
         <v>2948</v>
       </c>
-      <c r="H50" s="17"/>
-      <c r="J50" s="15"/>
-      <c r="K50" s="15"/>
-      <c r="L50" s="8"/>
+      <c r="H50" s="19"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="14"/>
+      <c r="L50" s="14"/>
+      <c r="M50" s="14"/>
+      <c r="N50" s="14"/>
+      <c r="R50" s="13"/>
+      <c r="S50" s="13"/>
     </row>
     <row r="51" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="21" t="s">
+      <c r="A51" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="B51" s="22" t="s">
+      <c r="B51" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="C51" s="23" t="n">
+      <c r="C51" s="25" t="n">
         <v>0.45</v>
       </c>
-      <c r="D51" s="23" t="n">
+      <c r="D51" s="25" t="n">
         <v>0.31</v>
       </c>
-      <c r="E51" s="23" t="n">
+      <c r="E51" s="25" t="n">
         <v>0.14</v>
       </c>
-      <c r="F51" s="23" t="n">
+      <c r="F51" s="25" t="n">
         <v>0.1</v>
       </c>
-      <c r="G51" s="24" t="n">
+      <c r="G51" s="26" t="n">
         <v>1100</v>
       </c>
-      <c r="H51" s="20"/>
-      <c r="J51" s="15"/>
-      <c r="K51" s="15"/>
-      <c r="L51" s="8"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="12"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="14"/>
+      <c r="M51" s="14"/>
+      <c r="N51" s="14"/>
     </row>
     <row r="52" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
@@ -3009,8 +3285,13 @@
       <c r="G52" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H52" s="16"/>
-      <c r="L52" s="8"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="13"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="14"/>
+      <c r="M52" s="14"/>
+      <c r="N52" s="14"/>
     </row>
     <row r="53" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
@@ -3034,8 +3315,13 @@
       <c r="G53" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H53" s="17"/>
-      <c r="L53" s="8"/>
+      <c r="H53" s="19"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="13"/>
+      <c r="K53" s="14"/>
+      <c r="L53" s="14"/>
+      <c r="M53" s="14"/>
+      <c r="N53" s="14"/>
     </row>
     <row r="54" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
@@ -3047,20 +3333,25 @@
       <c r="C54" s="10" t="n">
         <v>0.43</v>
       </c>
-      <c r="D54" s="13" t="n">
+      <c r="D54" s="16" t="n">
         <v>0.295</v>
       </c>
       <c r="E54" s="10" t="n">
         <v>0.13</v>
       </c>
-      <c r="F54" s="13" t="n">
+      <c r="F54" s="16" t="n">
         <v>0.145</v>
       </c>
       <c r="G54" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H54" s="17"/>
-      <c r="L54" s="8"/>
+      <c r="H54" s="19"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="14"/>
+      <c r="L54" s="14"/>
+      <c r="M54" s="14"/>
+      <c r="N54" s="14"/>
     </row>
     <row r="55" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
@@ -3084,8 +3375,13 @@
       <c r="G55" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H55" s="16"/>
-      <c r="L55" s="8"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="12"/>
+      <c r="J55" s="13"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="14"/>
+      <c r="M55" s="14"/>
+      <c r="N55" s="14"/>
     </row>
     <row r="56" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
@@ -3109,8 +3405,13 @@
       <c r="G56" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H56" s="17"/>
-      <c r="L56" s="8"/>
+      <c r="H56" s="19"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="13"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="14"/>
+      <c r="M56" s="14"/>
+      <c r="N56" s="14"/>
     </row>
     <row r="57" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
@@ -3134,8 +3435,13 @@
       <c r="G57" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H57" s="17"/>
-      <c r="L57" s="8"/>
+      <c r="H57" s="19"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="13"/>
+      <c r="K57" s="14"/>
+      <c r="L57" s="14"/>
+      <c r="M57" s="14"/>
+      <c r="N57" s="14"/>
     </row>
     <row r="58" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
@@ -3144,10 +3450,10 @@
       <c r="B58" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C58" s="13" t="n">
+      <c r="C58" s="16" t="n">
         <v>0.435</v>
       </c>
-      <c r="D58" s="13" t="n">
+      <c r="D58" s="16" t="n">
         <v>0.295</v>
       </c>
       <c r="E58" s="10" t="n">
@@ -3159,8 +3465,13 @@
       <c r="G58" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H58" s="16"/>
-      <c r="L58" s="8"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="12"/>
+      <c r="J58" s="13"/>
+      <c r="K58" s="14"/>
+      <c r="L58" s="14"/>
+      <c r="M58" s="14"/>
+      <c r="N58" s="14"/>
     </row>
     <row r="59" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
@@ -3184,23 +3495,28 @@
       <c r="G59" s="8" t="n">
         <v>1100</v>
       </c>
-      <c r="H59" s="14"/>
-      <c r="L59" s="8"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="12"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="14"/>
+      <c r="M59" s="14"/>
+      <c r="N59" s="14"/>
     </row>
     <row r="60" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="12" t="n">
+      <c r="A60" s="15" t="n">
         <v>42411</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C60" s="13" t="n">
+      <c r="C60" s="16" t="n">
         <v>0.481</v>
       </c>
-      <c r="D60" s="13" t="n">
+      <c r="D60" s="16" t="n">
         <v>0.328</v>
       </c>
-      <c r="E60" s="13" t="n">
+      <c r="E60" s="16" t="n">
         <v>0.101</v>
       </c>
       <c r="F60" s="10" t="n">
@@ -3209,8 +3525,13 @@
       <c r="G60" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H60" s="16"/>
-      <c r="L60" s="8"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="12"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="14"/>
+      <c r="L60" s="14"/>
+      <c r="M60" s="14"/>
+      <c r="N60" s="14"/>
     </row>
     <row r="61" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
@@ -3234,8 +3555,13 @@
       <c r="G61" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H61" s="16"/>
-      <c r="L61" s="8"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="12"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="14"/>
+      <c r="L61" s="14"/>
+      <c r="M61" s="14"/>
+      <c r="N61" s="14"/>
     </row>
     <row r="62" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
@@ -3244,7 +3570,7 @@
       <c r="B62" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C62" s="13" t="n">
+      <c r="C62" s="16" t="n">
         <v>0.435</v>
       </c>
       <c r="D62" s="10" t="n">
@@ -3253,14 +3579,19 @@
       <c r="E62" s="10" t="n">
         <v>0.16</v>
       </c>
-      <c r="F62" s="13" t="n">
+      <c r="F62" s="16" t="n">
         <v>0.115</v>
       </c>
       <c r="G62" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H62" s="16"/>
-      <c r="L62" s="8"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="13"/>
+      <c r="K62" s="14"/>
+      <c r="L62" s="14"/>
+      <c r="M62" s="14"/>
+      <c r="N62" s="14"/>
     </row>
     <row r="63" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
@@ -3284,8 +3615,13 @@
       <c r="G63" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H63" s="14"/>
-      <c r="L63" s="8"/>
+      <c r="H63" s="17"/>
+      <c r="I63" s="12"/>
+      <c r="J63" s="13"/>
+      <c r="K63" s="14"/>
+      <c r="L63" s="14"/>
+      <c r="M63" s="14"/>
+      <c r="N63" s="14"/>
     </row>
     <row r="64" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
@@ -3294,7 +3630,7 @@
       <c r="B64" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C64" s="13" t="n">
+      <c r="C64" s="16" t="n">
         <v>0.435</v>
       </c>
       <c r="D64" s="10" t="n">
@@ -3303,39 +3639,49 @@
       <c r="E64" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="F64" s="13" t="n">
+      <c r="F64" s="16" t="n">
         <v>0.135</v>
       </c>
       <c r="G64" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H64" s="16"/>
-      <c r="L64" s="8"/>
+      <c r="H64" s="18"/>
+      <c r="I64" s="12"/>
+      <c r="J64" s="13"/>
+      <c r="K64" s="14"/>
+      <c r="L64" s="14"/>
+      <c r="M64" s="14"/>
+      <c r="N64" s="14"/>
     </row>
     <row r="65" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="12" t="n">
+      <c r="A65" s="15" t="n">
         <v>42390</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="C65" s="13" t="n">
+      <c r="C65" s="16" t="n">
         <v>0.485</v>
       </c>
-      <c r="D65" s="13" t="n">
+      <c r="D65" s="16" t="n">
         <v>0.318</v>
       </c>
-      <c r="E65" s="13" t="n">
+      <c r="E65" s="16" t="n">
         <v>0.108</v>
       </c>
-      <c r="F65" s="13" t="n">
+      <c r="F65" s="16" t="n">
         <v>0.091</v>
       </c>
       <c r="G65" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H65" s="16"/>
-      <c r="L65" s="8"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="12"/>
+      <c r="J65" s="13"/>
+      <c r="K65" s="14"/>
+      <c r="L65" s="14"/>
+      <c r="M65" s="14"/>
+      <c r="N65" s="14"/>
     </row>
     <row r="66" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
@@ -3359,8 +3705,13 @@
       <c r="G66" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H66" s="16"/>
-      <c r="L66" s="8"/>
+      <c r="H66" s="18"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="14"/>
+      <c r="L66" s="14"/>
+      <c r="M66" s="14"/>
+      <c r="N66" s="14"/>
     </row>
     <row r="67" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
@@ -3384,11 +3735,16 @@
       <c r="G67" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H67" s="16"/>
-      <c r="L67" s="8"/>
+      <c r="H67" s="18"/>
+      <c r="I67" s="12"/>
+      <c r="J67" s="13"/>
+      <c r="K67" s="14"/>
+      <c r="L67" s="14"/>
+      <c r="M67" s="14"/>
+      <c r="N67" s="14"/>
     </row>
     <row r="68" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="12" t="n">
+      <c r="A68" s="15" t="n">
         <v>42353</v>
       </c>
       <c r="B68" s="9" t="s">
@@ -3409,8 +3765,13 @@
       <c r="G68" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H68" s="16"/>
-      <c r="L68" s="8"/>
+      <c r="H68" s="18"/>
+      <c r="I68" s="12"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="14"/>
+      <c r="L68" s="14"/>
+      <c r="M68" s="14"/>
+      <c r="N68" s="14"/>
     </row>
     <row r="69" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
@@ -3425,20 +3786,25 @@
       <c r="D69" s="10" t="n">
         <v>0.27</v>
       </c>
-      <c r="E69" s="13" t="n">
+      <c r="E69" s="16" t="n">
         <v>0.145</v>
       </c>
-      <c r="F69" s="13" t="n">
+      <c r="F69" s="16" t="n">
         <v>0.105</v>
       </c>
       <c r="G69" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H69" s="16"/>
-      <c r="L69" s="8"/>
+      <c r="H69" s="18"/>
+      <c r="I69" s="12"/>
+      <c r="J69" s="13"/>
+      <c r="K69" s="14"/>
+      <c r="L69" s="14"/>
+      <c r="M69" s="14"/>
+      <c r="N69" s="14"/>
     </row>
     <row r="70" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="12" t="n">
+      <c r="A70" s="15" t="n">
         <v>42346</v>
       </c>
       <c r="B70" s="9" t="s">
@@ -3459,8 +3825,13 @@
       <c r="G70" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H70" s="14"/>
-      <c r="L70" s="8"/>
+      <c r="H70" s="17"/>
+      <c r="I70" s="12"/>
+      <c r="J70" s="13"/>
+      <c r="K70" s="14"/>
+      <c r="L70" s="14"/>
+      <c r="M70" s="14"/>
+      <c r="N70" s="14"/>
     </row>
     <row r="71" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
@@ -3484,11 +3855,16 @@
       <c r="G71" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H71" s="16"/>
-      <c r="L71" s="8"/>
+      <c r="H71" s="18"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="13"/>
+      <c r="K71" s="14"/>
+      <c r="L71" s="14"/>
+      <c r="M71" s="14"/>
+      <c r="N71" s="14"/>
     </row>
     <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="12" t="n">
+      <c r="A72" s="15" t="n">
         <v>42339</v>
       </c>
       <c r="B72" s="9" t="s">
@@ -3509,8 +3885,13 @@
       <c r="G72" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H72" s="16"/>
-      <c r="L72" s="8"/>
+      <c r="H72" s="18"/>
+      <c r="I72" s="12"/>
+      <c r="J72" s="13"/>
+      <c r="K72" s="14"/>
+      <c r="L72" s="14"/>
+      <c r="M72" s="14"/>
+      <c r="N72" s="14"/>
     </row>
     <row r="73" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
@@ -3519,10 +3900,10 @@
       <c r="B73" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="C73" s="13" t="n">
+      <c r="C73" s="16" t="n">
         <v>0.465</v>
       </c>
-      <c r="D73" s="13" t="n">
+      <c r="D73" s="16" t="n">
         <v>0.285</v>
       </c>
       <c r="E73" s="10" t="n">
@@ -3534,36 +3915,46 @@
       <c r="G73" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H73" s="16"/>
-      <c r="L73" s="8"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="12"/>
+      <c r="J73" s="13"/>
+      <c r="K73" s="14"/>
+      <c r="L73" s="14"/>
+      <c r="M73" s="14"/>
+      <c r="N73" s="14"/>
     </row>
     <row r="74" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="12" t="n">
+      <c r="A74" s="15" t="n">
         <v>42334</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="C74" s="13" t="n">
+      <c r="C74" s="16" t="n">
         <v>0.488</v>
       </c>
-      <c r="D74" s="13" t="n">
+      <c r="D74" s="16" t="n">
         <v>0.311</v>
       </c>
-      <c r="E74" s="13" t="n">
+      <c r="E74" s="16" t="n">
         <v>0.112</v>
       </c>
-      <c r="F74" s="13" t="n">
+      <c r="F74" s="16" t="n">
         <v>0.089</v>
       </c>
       <c r="G74" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H74" s="16"/>
-      <c r="L74" s="8"/>
+      <c r="H74" s="18"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="13"/>
+      <c r="K74" s="14"/>
+      <c r="L74" s="14"/>
+      <c r="M74" s="14"/>
+      <c r="N74" s="14"/>
     </row>
     <row r="75" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="12" t="n">
+      <c r="A75" s="15" t="n">
         <v>42332</v>
       </c>
       <c r="B75" s="9" t="s">
@@ -3584,8 +3975,13 @@
       <c r="G75" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H75" s="16"/>
-      <c r="L75" s="8"/>
+      <c r="H75" s="18"/>
+      <c r="I75" s="12"/>
+      <c r="J75" s="13"/>
+      <c r="K75" s="14"/>
+      <c r="L75" s="14"/>
+      <c r="M75" s="14"/>
+      <c r="N75" s="14"/>
     </row>
     <row r="76" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
@@ -3609,8 +4005,13 @@
       <c r="G76" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H76" s="16"/>
-      <c r="L76" s="8"/>
+      <c r="H76" s="18"/>
+      <c r="I76" s="12"/>
+      <c r="J76" s="13"/>
+      <c r="K76" s="14"/>
+      <c r="L76" s="14"/>
+      <c r="M76" s="14"/>
+      <c r="N76" s="14"/>
     </row>
     <row r="77" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
@@ -3625,23 +4026,28 @@
       <c r="D77" s="10" t="n">
         <v>0.28</v>
       </c>
-      <c r="E77" s="13" t="n">
+      <c r="E77" s="16" t="n">
         <v>0.145</v>
       </c>
-      <c r="F77" s="13" t="n">
+      <c r="F77" s="16" t="n">
         <v>0.115</v>
       </c>
       <c r="G77" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H77" s="16"/>
-      <c r="L77" s="8"/>
+      <c r="H77" s="18"/>
+      <c r="I77" s="12"/>
+      <c r="J77" s="13"/>
+      <c r="K77" s="14"/>
+      <c r="L77" s="14"/>
+      <c r="M77" s="14"/>
+      <c r="N77" s="14"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B78" s="18" t="s">
+      <c r="B78" s="20" t="s">
         <v>138</v>
       </c>
       <c r="C78" s="10" t="n">
@@ -3659,11 +4065,16 @@
       <c r="G78" s="8" t="n">
         <v>1100</v>
       </c>
-      <c r="H78" s="16"/>
-      <c r="L78" s="8"/>
+      <c r="H78" s="18"/>
+      <c r="I78" s="12"/>
+      <c r="J78" s="13"/>
+      <c r="K78" s="14"/>
+      <c r="L78" s="14"/>
+      <c r="M78" s="14"/>
+      <c r="N78" s="14"/>
     </row>
     <row r="79" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="12" t="n">
+      <c r="A79" s="15" t="n">
         <v>42318</v>
       </c>
       <c r="B79" s="9" t="s">
@@ -3684,8 +4095,13 @@
       <c r="G79" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H79" s="16"/>
-      <c r="L79" s="8"/>
+      <c r="H79" s="18"/>
+      <c r="I79" s="12"/>
+      <c r="J79" s="13"/>
+      <c r="K79" s="14"/>
+      <c r="L79" s="14"/>
+      <c r="M79" s="14"/>
+      <c r="N79" s="14"/>
     </row>
     <row r="80" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
@@ -3709,14 +4125,19 @@
       <c r="G80" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H80" s="16"/>
-      <c r="L80" s="8"/>
+      <c r="H80" s="18"/>
+      <c r="I80" s="12"/>
+      <c r="J80" s="13"/>
+      <c r="K80" s="14"/>
+      <c r="L80" s="14"/>
+      <c r="M80" s="14"/>
+      <c r="N80" s="14"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="12" t="n">
+      <c r="A81" s="15" t="n">
         <v>42311</v>
       </c>
-      <c r="B81" s="18" t="s">
+      <c r="B81" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C81" s="10" t="n">
@@ -3734,8 +4155,13 @@
       <c r="G81" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H81" s="16"/>
-      <c r="L81" s="8"/>
+      <c r="H81" s="18"/>
+      <c r="I81" s="12"/>
+      <c r="J81" s="13"/>
+      <c r="K81" s="14"/>
+      <c r="L81" s="14"/>
+      <c r="M81" s="14"/>
+      <c r="N81" s="14"/>
     </row>
     <row r="82" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
@@ -3747,10 +4173,10 @@
       <c r="C82" s="10" t="n">
         <v>0.47</v>
       </c>
-      <c r="D82" s="13" t="n">
+      <c r="D82" s="16" t="n">
         <v>0.285</v>
       </c>
-      <c r="E82" s="13" t="n">
+      <c r="E82" s="16" t="n">
         <v>0.145</v>
       </c>
       <c r="F82" s="10" t="n">
@@ -3759,11 +4185,16 @@
       <c r="G82" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H82" s="16"/>
-      <c r="L82" s="8"/>
+      <c r="H82" s="18"/>
+      <c r="I82" s="12"/>
+      <c r="J82" s="13"/>
+      <c r="K82" s="14"/>
+      <c r="L82" s="14"/>
+      <c r="M82" s="14"/>
+      <c r="N82" s="14"/>
     </row>
     <row r="83" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="12" t="n">
+      <c r="A83" s="15" t="n">
         <v>42304</v>
       </c>
       <c r="B83" s="9" t="s">
@@ -3784,8 +4215,13 @@
       <c r="G83" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H83" s="14"/>
-      <c r="L83" s="8"/>
+      <c r="H83" s="17"/>
+      <c r="I83" s="12"/>
+      <c r="J83" s="13"/>
+      <c r="K83" s="14"/>
+      <c r="L83" s="14"/>
+      <c r="M83" s="14"/>
+      <c r="N83" s="14"/>
     </row>
     <row r="84" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
@@ -3809,36 +4245,46 @@
       <c r="G84" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H84" s="16"/>
-      <c r="L84" s="8"/>
+      <c r="H84" s="18"/>
+      <c r="I84" s="12"/>
+      <c r="J84" s="13"/>
+      <c r="K84" s="14"/>
+      <c r="L84" s="14"/>
+      <c r="M84" s="14"/>
+      <c r="N84" s="14"/>
     </row>
     <row r="85" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="12" t="n">
+      <c r="A85" s="15" t="n">
         <v>42299</v>
       </c>
       <c r="B85" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="C85" s="13" t="n">
+      <c r="C85" s="16" t="n">
         <v>0.467</v>
       </c>
-      <c r="D85" s="13" t="n">
+      <c r="D85" s="16" t="n">
         <v>0.33</v>
       </c>
-      <c r="E85" s="13" t="n">
+      <c r="E85" s="16" t="n">
         <v>0.113</v>
       </c>
-      <c r="F85" s="13" t="n">
+      <c r="F85" s="16" t="n">
         <v>0.091</v>
       </c>
       <c r="G85" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H85" s="16"/>
-      <c r="L85" s="8"/>
+      <c r="H85" s="18"/>
+      <c r="I85" s="12"/>
+      <c r="J85" s="13"/>
+      <c r="K85" s="14"/>
+      <c r="L85" s="14"/>
+      <c r="M85" s="14"/>
+      <c r="N85" s="14"/>
     </row>
     <row r="86" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="12" t="n">
+      <c r="A86" s="15" t="n">
         <v>42297</v>
       </c>
       <c r="B86" s="9" t="s">
@@ -3859,8 +4305,13 @@
       <c r="G86" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H86" s="16"/>
-      <c r="L86" s="8"/>
+      <c r="H86" s="18"/>
+      <c r="I86" s="12"/>
+      <c r="J86" s="13"/>
+      <c r="K86" s="14"/>
+      <c r="L86" s="14"/>
+      <c r="M86" s="14"/>
+      <c r="N86" s="14"/>
     </row>
     <row r="87" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
@@ -3869,23 +4320,28 @@
       <c r="B87" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="C87" s="13" t="n">
+      <c r="C87" s="16" t="n">
         <v>0.465</v>
       </c>
-      <c r="D87" s="13" t="n">
+      <c r="D87" s="16" t="n">
         <v>0.275</v>
       </c>
-      <c r="E87" s="13" t="n">
+      <c r="E87" s="16" t="n">
         <v>0.155</v>
       </c>
-      <c r="F87" s="13" t="n">
+      <c r="F87" s="16" t="n">
         <v>0.105</v>
       </c>
       <c r="G87" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H87" s="16"/>
-      <c r="L87" s="8"/>
+      <c r="H87" s="18"/>
+      <c r="I87" s="12"/>
+      <c r="J87" s="13"/>
+      <c r="K87" s="14"/>
+      <c r="L87" s="14"/>
+      <c r="M87" s="14"/>
+      <c r="N87" s="14"/>
     </row>
     <row r="88" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
@@ -3909,11 +4365,16 @@
       <c r="G88" s="8" t="n">
         <v>1100</v>
       </c>
-      <c r="H88" s="16"/>
-      <c r="L88" s="8"/>
+      <c r="H88" s="18"/>
+      <c r="I88" s="12"/>
+      <c r="J88" s="13"/>
+      <c r="K88" s="14"/>
+      <c r="L88" s="14"/>
+      <c r="M88" s="14"/>
+      <c r="N88" s="14"/>
     </row>
     <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="12" t="n">
+      <c r="A89" s="15" t="n">
         <v>42290</v>
       </c>
       <c r="B89" s="9" t="s">
@@ -3934,8 +4395,13 @@
       <c r="G89" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H89" s="16"/>
-      <c r="L89" s="8"/>
+      <c r="H89" s="18"/>
+      <c r="I89" s="12"/>
+      <c r="J89" s="13"/>
+      <c r="K89" s="14"/>
+      <c r="L89" s="14"/>
+      <c r="M89" s="14"/>
+      <c r="N89" s="14"/>
     </row>
     <row r="90" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
@@ -3959,8 +4425,13 @@
       <c r="G90" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H90" s="16"/>
-      <c r="L90" s="8"/>
+      <c r="H90" s="18"/>
+      <c r="I90" s="12"/>
+      <c r="J90" s="13"/>
+      <c r="K90" s="14"/>
+      <c r="L90" s="14"/>
+      <c r="M90" s="14"/>
+      <c r="N90" s="14"/>
     </row>
     <row r="91" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
@@ -3972,20 +4443,25 @@
       <c r="C91" s="10" t="n">
         <v>0.47</v>
       </c>
-      <c r="D91" s="13" t="n">
+      <c r="D91" s="16" t="n">
         <v>0.275</v>
       </c>
       <c r="E91" s="10" t="n">
         <v>0.14</v>
       </c>
-      <c r="F91" s="13" t="n">
+      <c r="F91" s="16" t="n">
         <v>0.115</v>
       </c>
       <c r="G91" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H91" s="17"/>
-      <c r="L91" s="8"/>
+      <c r="H91" s="19"/>
+      <c r="I91" s="12"/>
+      <c r="J91" s="13"/>
+      <c r="K91" s="14"/>
+      <c r="L91" s="14"/>
+      <c r="M91" s="14"/>
+      <c r="N91" s="14"/>
     </row>
     <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
@@ -4009,14 +4485,19 @@
       <c r="G92" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H92" s="16"/>
-      <c r="L92" s="8"/>
+      <c r="H92" s="18"/>
+      <c r="I92" s="12"/>
+      <c r="J92" s="13"/>
+      <c r="K92" s="14"/>
+      <c r="L92" s="14"/>
+      <c r="M92" s="14"/>
+      <c r="N92" s="14"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B93" s="18" t="s">
+      <c r="B93" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C93" s="10" t="n">
@@ -4034,8 +4515,13 @@
       <c r="G93" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H93" s="16"/>
-      <c r="L93" s="8"/>
+      <c r="H93" s="18"/>
+      <c r="I93" s="12"/>
+      <c r="J93" s="13"/>
+      <c r="K93" s="14"/>
+      <c r="L93" s="14"/>
+      <c r="M93" s="14"/>
+      <c r="N93" s="14"/>
     </row>
     <row r="94" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
@@ -4059,8 +4545,13 @@
       <c r="G94" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H94" s="16"/>
-      <c r="L94" s="8"/>
+      <c r="H94" s="18"/>
+      <c r="I94" s="12"/>
+      <c r="J94" s="13"/>
+      <c r="K94" s="14"/>
+      <c r="L94" s="14"/>
+      <c r="M94" s="14"/>
+      <c r="N94" s="14"/>
     </row>
     <row r="95" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
@@ -4072,20 +4563,25 @@
       <c r="C95" s="10" t="n">
         <v>0.46</v>
       </c>
-      <c r="D95" s="13" t="n">
+      <c r="D95" s="16" t="n">
         <v>0.295</v>
       </c>
       <c r="E95" s="10" t="n">
         <v>0.13</v>
       </c>
-      <c r="F95" s="13" t="n">
+      <c r="F95" s="16" t="n">
         <v>0.115</v>
       </c>
       <c r="G95" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H95" s="17"/>
-      <c r="L95" s="8"/>
+      <c r="H95" s="19"/>
+      <c r="I95" s="12"/>
+      <c r="J95" s="13"/>
+      <c r="K95" s="14"/>
+      <c r="L95" s="14"/>
+      <c r="M95" s="14"/>
+      <c r="N95" s="14"/>
     </row>
     <row r="96" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
@@ -4109,8 +4605,13 @@
       <c r="G96" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H96" s="16"/>
-      <c r="L96" s="8"/>
+      <c r="H96" s="18"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="13"/>
+      <c r="K96" s="14"/>
+      <c r="L96" s="14"/>
+      <c r="M96" s="14"/>
+      <c r="N96" s="14"/>
     </row>
     <row r="97" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
@@ -4134,33 +4635,43 @@
       <c r="G97" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H97" s="16"/>
-      <c r="L97" s="8"/>
+      <c r="H97" s="18"/>
+      <c r="I97" s="12"/>
+      <c r="J97" s="13"/>
+      <c r="K97" s="14"/>
+      <c r="L97" s="14"/>
+      <c r="M97" s="14"/>
+      <c r="N97" s="14"/>
     </row>
     <row r="98" customFormat="false" ht="24.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="12" t="n">
+      <c r="A98" s="15" t="n">
         <v>42262</v>
       </c>
-      <c r="B98" s="18" t="s">
+      <c r="B98" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C98" s="13" t="n">
+      <c r="C98" s="16" t="n">
         <v>0.433</v>
       </c>
-      <c r="D98" s="13" t="n">
+      <c r="D98" s="16" t="n">
         <v>0.359</v>
       </c>
-      <c r="E98" s="13" t="n">
+      <c r="E98" s="16" t="n">
         <v>0.119</v>
       </c>
-      <c r="F98" s="13" t="n">
+      <c r="F98" s="16" t="n">
         <v>0.089</v>
       </c>
       <c r="G98" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H98" s="16"/>
-      <c r="L98" s="8"/>
+      <c r="H98" s="18"/>
+      <c r="I98" s="12"/>
+      <c r="J98" s="13"/>
+      <c r="K98" s="14"/>
+      <c r="L98" s="14"/>
+      <c r="M98" s="14"/>
+      <c r="N98" s="14"/>
     </row>
     <row r="99" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
@@ -4172,20 +4683,25 @@
       <c r="C99" s="10" t="n">
         <v>0.35</v>
       </c>
-      <c r="D99" s="13" t="n">
+      <c r="D99" s="16" t="n">
         <v>0.365</v>
       </c>
       <c r="E99" s="10" t="n">
         <v>0.16</v>
       </c>
-      <c r="F99" s="13" t="n">
+      <c r="F99" s="16" t="n">
         <v>0.125</v>
       </c>
       <c r="G99" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H99" s="17"/>
-      <c r="L99" s="8"/>
+      <c r="H99" s="19"/>
+      <c r="I99" s="27"/>
+      <c r="J99" s="13"/>
+      <c r="K99" s="14"/>
+      <c r="L99" s="14"/>
+      <c r="M99" s="14"/>
+      <c r="N99" s="14"/>
     </row>
     <row r="100" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
@@ -4194,23 +4710,28 @@
       <c r="B100" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C100" s="13" t="n">
+      <c r="C100" s="16" t="n">
         <v>0.365</v>
       </c>
-      <c r="D100" s="13" t="n">
+      <c r="D100" s="16" t="n">
         <v>0.355</v>
       </c>
-      <c r="E100" s="13" t="n">
+      <c r="E100" s="16" t="n">
         <v>0.165</v>
       </c>
-      <c r="F100" s="13" t="n">
+      <c r="F100" s="16" t="n">
         <v>0.115</v>
       </c>
       <c r="G100" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H100" s="17"/>
-      <c r="L100" s="8"/>
+      <c r="H100" s="19"/>
+      <c r="I100" s="12"/>
+      <c r="J100" s="13"/>
+      <c r="K100" s="14"/>
+      <c r="L100" s="14"/>
+      <c r="M100" s="14"/>
+      <c r="N100" s="14"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
@@ -4234,8 +4755,13 @@
       <c r="G101" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H101" s="17"/>
-      <c r="L101" s="8"/>
+      <c r="H101" s="19"/>
+      <c r="I101" s="12"/>
+      <c r="J101" s="13"/>
+      <c r="K101" s="14"/>
+      <c r="L101" s="14"/>
+      <c r="M101" s="14"/>
+      <c r="N101" s="14"/>
     </row>
     <row r="102" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
@@ -4259,33 +4785,43 @@
       <c r="G102" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H102" s="17"/>
-      <c r="L102" s="8"/>
+      <c r="H102" s="19"/>
+      <c r="I102" s="12"/>
+      <c r="J102" s="13"/>
+      <c r="K102" s="14"/>
+      <c r="L102" s="14"/>
+      <c r="M102" s="14"/>
+      <c r="N102" s="14"/>
     </row>
     <row r="103" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="12" t="n">
+      <c r="A103" s="15" t="n">
         <v>42243</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="C103" s="13" t="n">
+      <c r="C103" s="16" t="n">
         <v>0.403</v>
       </c>
-      <c r="D103" s="13" t="n">
+      <c r="D103" s="16" t="n">
         <v>0.375</v>
       </c>
-      <c r="E103" s="13" t="n">
+      <c r="E103" s="16" t="n">
         <v>0.134</v>
       </c>
-      <c r="F103" s="13" t="n">
+      <c r="F103" s="16" t="n">
         <v>0.089</v>
       </c>
       <c r="G103" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H103" s="17"/>
-      <c r="L103" s="8"/>
+      <c r="H103" s="19"/>
+      <c r="I103" s="12"/>
+      <c r="J103" s="13"/>
+      <c r="K103" s="14"/>
+      <c r="L103" s="14"/>
+      <c r="M103" s="14"/>
+      <c r="N103" s="14"/>
     </row>
     <row r="104" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
@@ -4294,7 +4830,7 @@
       <c r="B104" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="C104" s="13" t="n">
+      <c r="C104" s="16" t="n">
         <v>0.385</v>
       </c>
       <c r="D104" s="10" t="n">
@@ -4303,14 +4839,19 @@
       <c r="E104" s="10" t="n">
         <v>0.14</v>
       </c>
-      <c r="F104" s="13" t="n">
+      <c r="F104" s="16" t="n">
         <v>0.115</v>
       </c>
       <c r="G104" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H104" s="17"/>
-      <c r="L104" s="8"/>
+      <c r="H104" s="19"/>
+      <c r="I104" s="12"/>
+      <c r="J104" s="13"/>
+      <c r="K104" s="14"/>
+      <c r="L104" s="14"/>
+      <c r="M104" s="14"/>
+      <c r="N104" s="14"/>
     </row>
     <row r="105" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
@@ -4334,8 +4875,13 @@
       <c r="G105" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H105" s="20"/>
-      <c r="L105" s="8"/>
+      <c r="H105" s="22"/>
+      <c r="I105" s="12"/>
+      <c r="J105" s="13"/>
+      <c r="K105" s="14"/>
+      <c r="L105" s="14"/>
+      <c r="M105" s="14"/>
+      <c r="N105" s="14"/>
     </row>
     <row r="106" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
@@ -4359,14 +4905,19 @@
       <c r="G106" s="8" t="n">
         <v>1100</v>
       </c>
-      <c r="H106" s="17"/>
-      <c r="L106" s="8"/>
+      <c r="H106" s="19"/>
+      <c r="I106" s="12"/>
+      <c r="J106" s="13"/>
+      <c r="K106" s="14"/>
+      <c r="L106" s="14"/>
+      <c r="M106" s="14"/>
+      <c r="N106" s="14"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B107" s="18" t="s">
+      <c r="B107" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C107" s="10" t="n">
@@ -4384,8 +4935,13 @@
       <c r="G107" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H107" s="17"/>
-      <c r="L107" s="8"/>
+      <c r="H107" s="19"/>
+      <c r="I107" s="12"/>
+      <c r="J107" s="13"/>
+      <c r="K107" s="14"/>
+      <c r="L107" s="14"/>
+      <c r="M107" s="14"/>
+      <c r="N107" s="14"/>
     </row>
     <row r="108" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
@@ -4394,13 +4950,13 @@
       <c r="B108" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="C108" s="13" t="n">
+      <c r="C108" s="16" t="n">
         <v>0.365</v>
       </c>
       <c r="D108" s="10" t="n">
         <v>0.37</v>
       </c>
-      <c r="E108" s="13" t="n">
+      <c r="E108" s="16" t="n">
         <v>0.155</v>
       </c>
       <c r="F108" s="10" t="n">
@@ -4409,8 +4965,13 @@
       <c r="G108" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H108" s="17"/>
-      <c r="L108" s="8"/>
+      <c r="H108" s="19"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="13"/>
+      <c r="K108" s="14"/>
+      <c r="L108" s="14"/>
+      <c r="M108" s="14"/>
+      <c r="N108" s="14"/>
     </row>
     <row r="109" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
@@ -4434,14 +4995,19 @@
       <c r="G109" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H109" s="17"/>
-      <c r="L109" s="8"/>
+      <c r="H109" s="19"/>
+      <c r="I109" s="12"/>
+      <c r="J109" s="13"/>
+      <c r="K109" s="14"/>
+      <c r="L109" s="14"/>
+      <c r="M109" s="14"/>
+      <c r="N109" s="14"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B110" s="18" t="s">
+      <c r="B110" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C110" s="10" t="n">
@@ -4459,33 +5025,43 @@
       <c r="G110" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H110" s="17"/>
-      <c r="L110" s="8"/>
+      <c r="H110" s="19"/>
+      <c r="I110" s="12"/>
+      <c r="J110" s="13"/>
+      <c r="K110" s="14"/>
+      <c r="L110" s="14"/>
+      <c r="M110" s="14"/>
+      <c r="N110" s="14"/>
     </row>
     <row r="111" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="12" t="n">
+      <c r="A111" s="15" t="n">
         <v>42222</v>
       </c>
       <c r="B111" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C111" s="13" t="n">
+      <c r="C111" s="16" t="n">
         <v>0.402</v>
       </c>
-      <c r="D111" s="13" t="n">
+      <c r="D111" s="16" t="n">
         <v>0.383</v>
       </c>
-      <c r="E111" s="13" t="n">
+      <c r="E111" s="16" t="n">
         <v>0.128</v>
       </c>
-      <c r="F111" s="13" t="n">
+      <c r="F111" s="16" t="n">
         <v>0.087</v>
       </c>
       <c r="G111" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H111" s="17"/>
-      <c r="L111" s="8"/>
+      <c r="H111" s="19"/>
+      <c r="I111" s="12"/>
+      <c r="J111" s="13"/>
+      <c r="K111" s="14"/>
+      <c r="L111" s="14"/>
+      <c r="M111" s="14"/>
+      <c r="N111" s="14"/>
     </row>
     <row r="112" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
@@ -4509,33 +5085,43 @@
       <c r="G112" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H112" s="17"/>
-      <c r="L112" s="8"/>
+      <c r="H112" s="19"/>
+      <c r="I112" s="12"/>
+      <c r="J112" s="13"/>
+      <c r="K112" s="14"/>
+      <c r="L112" s="14"/>
+      <c r="M112" s="14"/>
+      <c r="N112" s="14"/>
     </row>
     <row r="113" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="12" t="n">
+      <c r="A113" s="15" t="n">
         <v>42215</v>
       </c>
       <c r="B113" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="C113" s="13" t="n">
+      <c r="C113" s="16" t="n">
         <v>0.406</v>
       </c>
       <c r="D113" s="10" t="n">
         <v>0.38</v>
       </c>
-      <c r="E113" s="13" t="n">
+      <c r="E113" s="16" t="n">
         <v>0.129</v>
       </c>
-      <c r="F113" s="13" t="n">
+      <c r="F113" s="16" t="n">
         <v>0.086</v>
       </c>
       <c r="G113" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H113" s="17"/>
-      <c r="L113" s="8"/>
+      <c r="H113" s="19"/>
+      <c r="I113" s="12"/>
+      <c r="J113" s="13"/>
+      <c r="K113" s="14"/>
+      <c r="L113" s="14"/>
+      <c r="M113" s="14"/>
+      <c r="N113" s="14"/>
     </row>
     <row r="114" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
@@ -4547,20 +5133,25 @@
       <c r="C114" s="10" t="n">
         <v>0.39</v>
       </c>
-      <c r="D114" s="13" t="n">
+      <c r="D114" s="16" t="n">
         <v>0.355</v>
       </c>
       <c r="E114" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="F114" s="13" t="n">
+      <c r="F114" s="16" t="n">
         <v>0.105</v>
       </c>
       <c r="G114" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H114" s="17"/>
-      <c r="L114" s="8"/>
+      <c r="H114" s="19"/>
+      <c r="I114" s="12"/>
+      <c r="J114" s="13"/>
+      <c r="K114" s="14"/>
+      <c r="L114" s="14"/>
+      <c r="M114" s="14"/>
+      <c r="N114" s="14"/>
     </row>
     <row r="115" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
@@ -4584,14 +5175,19 @@
       <c r="G115" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H115" s="17"/>
-      <c r="L115" s="8"/>
+      <c r="H115" s="19"/>
+      <c r="I115" s="12"/>
+      <c r="J115" s="13"/>
+      <c r="K115" s="14"/>
+      <c r="L115" s="14"/>
+      <c r="M115" s="14"/>
+      <c r="N115" s="14"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B116" s="18" t="s">
+      <c r="B116" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C116" s="10" t="n">
@@ -4609,8 +5205,13 @@
       <c r="G116" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H116" s="17"/>
-      <c r="L116" s="8"/>
+      <c r="H116" s="19"/>
+      <c r="I116" s="12"/>
+      <c r="J116" s="13"/>
+      <c r="K116" s="14"/>
+      <c r="L116" s="14"/>
+      <c r="M116" s="14"/>
+      <c r="N116" s="14"/>
     </row>
     <row r="117" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
@@ -4619,23 +5220,28 @@
       <c r="B117" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="C117" s="13" t="n">
+      <c r="C117" s="16" t="n">
         <v>0.415</v>
       </c>
-      <c r="D117" s="13" t="n">
+      <c r="D117" s="16" t="n">
         <v>0.345</v>
       </c>
-      <c r="E117" s="13" t="n">
+      <c r="E117" s="16" t="n">
         <v>0.135</v>
       </c>
-      <c r="F117" s="13" t="n">
+      <c r="F117" s="16" t="n">
         <v>0.105</v>
       </c>
       <c r="G117" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H117" s="17"/>
-      <c r="L117" s="8"/>
+      <c r="H117" s="19"/>
+      <c r="I117" s="12"/>
+      <c r="J117" s="13"/>
+      <c r="K117" s="14"/>
+      <c r="L117" s="14"/>
+      <c r="M117" s="14"/>
+      <c r="N117" s="14"/>
     </row>
     <row r="118" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
@@ -4659,8 +5265,13 @@
       <c r="G118" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H118" s="17"/>
-      <c r="L118" s="8"/>
+      <c r="H118" s="19"/>
+      <c r="I118" s="12"/>
+      <c r="J118" s="13"/>
+      <c r="K118" s="14"/>
+      <c r="L118" s="14"/>
+      <c r="M118" s="14"/>
+      <c r="N118" s="14"/>
     </row>
     <row r="119" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
@@ -4684,8 +5295,13 @@
       <c r="G119" s="8" t="n">
         <v>1100</v>
       </c>
-      <c r="H119" s="17"/>
-      <c r="L119" s="8"/>
+      <c r="H119" s="19"/>
+      <c r="I119" s="12"/>
+      <c r="J119" s="13"/>
+      <c r="K119" s="14"/>
+      <c r="L119" s="14"/>
+      <c r="M119" s="14"/>
+      <c r="N119" s="14"/>
     </row>
     <row r="120" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
@@ -4709,11 +5325,16 @@
       <c r="G120" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H120" s="17"/>
-      <c r="L120" s="8"/>
+      <c r="H120" s="19"/>
+      <c r="I120" s="12"/>
+      <c r="J120" s="13"/>
+      <c r="K120" s="14"/>
+      <c r="L120" s="14"/>
+      <c r="M120" s="14"/>
+      <c r="N120" s="14"/>
     </row>
     <row r="121" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="12" t="n">
+      <c r="A121" s="15" t="n">
         <v>42171</v>
       </c>
       <c r="B121" s="9" t="s">
@@ -4734,14 +5355,19 @@
       <c r="G121" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H121" s="20"/>
-      <c r="L121" s="8"/>
+      <c r="H121" s="22"/>
+      <c r="I121" s="12"/>
+      <c r="J121" s="13"/>
+      <c r="K121" s="14"/>
+      <c r="L121" s="14"/>
+      <c r="M121" s="14"/>
+      <c r="N121" s="14"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="12" t="n">
+      <c r="A122" s="15" t="n">
         <v>42171</v>
       </c>
-      <c r="B122" s="18" t="s">
+      <c r="B122" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C122" s="10" t="n">
@@ -4759,8 +5385,13 @@
       <c r="G122" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H122" s="17"/>
-      <c r="L122" s="8"/>
+      <c r="H122" s="19"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="13"/>
+      <c r="K122" s="14"/>
+      <c r="L122" s="14"/>
+      <c r="M122" s="14"/>
+      <c r="N122" s="14"/>
     </row>
     <row r="123" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
@@ -4769,23 +5400,28 @@
       <c r="B123" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C123" s="13" t="n">
+      <c r="C123" s="16" t="n">
         <v>0.375</v>
       </c>
-      <c r="D123" s="13" t="n">
+      <c r="D123" s="16" t="n">
         <v>0.375</v>
       </c>
-      <c r="E123" s="13" t="n">
+      <c r="E123" s="16" t="n">
         <v>0.135</v>
       </c>
-      <c r="F123" s="13" t="n">
+      <c r="F123" s="16" t="n">
         <v>0.115</v>
       </c>
       <c r="G123" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H123" s="17"/>
-      <c r="L123" s="8"/>
+      <c r="H123" s="19"/>
+      <c r="I123" s="12"/>
+      <c r="J123" s="13"/>
+      <c r="K123" s="14"/>
+      <c r="L123" s="14"/>
+      <c r="M123" s="14"/>
+      <c r="N123" s="14"/>
     </row>
     <row r="124" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
@@ -4809,14 +5445,19 @@
       <c r="G124" s="8" t="n">
         <v>1100</v>
       </c>
-      <c r="H124" s="20"/>
-      <c r="L124" s="8"/>
+      <c r="H124" s="22"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="13"/>
+      <c r="K124" s="14"/>
+      <c r="L124" s="14"/>
+      <c r="M124" s="14"/>
+      <c r="N124" s="14"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B125" s="18" t="s">
+      <c r="B125" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C125" s="10" t="n">
@@ -4834,11 +5475,16 @@
       <c r="G125" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H125" s="17"/>
-      <c r="L125" s="8"/>
+      <c r="H125" s="19"/>
+      <c r="I125" s="12"/>
+      <c r="J125" s="13"/>
+      <c r="K125" s="14"/>
+      <c r="L125" s="14"/>
+      <c r="M125" s="14"/>
+      <c r="N125" s="14"/>
     </row>
     <row r="126" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="12" t="n">
+      <c r="A126" s="15" t="n">
         <v>42157</v>
       </c>
       <c r="B126" s="9" t="s">
@@ -4859,11 +5505,16 @@
       <c r="G126" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H126" s="17"/>
-      <c r="L126" s="8"/>
+      <c r="H126" s="19"/>
+      <c r="I126" s="12"/>
+      <c r="J126" s="13"/>
+      <c r="K126" s="14"/>
+      <c r="L126" s="14"/>
+      <c r="M126" s="14"/>
+      <c r="N126" s="14"/>
     </row>
     <row r="127" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="12" t="n">
+      <c r="A127" s="15" t="n">
         <v>42157</v>
       </c>
       <c r="B127" s="9" t="s">
@@ -4884,8 +5535,13 @@
       <c r="G127" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H127" s="17"/>
-      <c r="L127" s="8"/>
+      <c r="H127" s="19"/>
+      <c r="I127" s="12"/>
+      <c r="J127" s="13"/>
+      <c r="K127" s="14"/>
+      <c r="L127" s="14"/>
+      <c r="M127" s="14"/>
+      <c r="N127" s="14"/>
     </row>
     <row r="128" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
@@ -4909,11 +5565,16 @@
       <c r="G128" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H128" s="17"/>
-      <c r="L128" s="8"/>
+      <c r="H128" s="19"/>
+      <c r="I128" s="12"/>
+      <c r="J128" s="13"/>
+      <c r="K128" s="14"/>
+      <c r="L128" s="14"/>
+      <c r="M128" s="14"/>
+      <c r="N128" s="14"/>
     </row>
     <row r="129" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="12" t="n">
+      <c r="A129" s="15" t="n">
         <v>42150</v>
       </c>
       <c r="B129" s="9" t="s">
@@ -4934,36 +5595,46 @@
       <c r="G129" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H129" s="17"/>
-      <c r="L129" s="8"/>
+      <c r="H129" s="19"/>
+      <c r="I129" s="12"/>
+      <c r="J129" s="13"/>
+      <c r="K129" s="14"/>
+      <c r="L129" s="14"/>
+      <c r="M129" s="14"/>
+      <c r="N129" s="14"/>
     </row>
     <row r="130" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="12" t="n">
+      <c r="A130" s="15" t="n">
         <v>42142</v>
       </c>
       <c r="B130" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="C130" s="13" t="n">
+      <c r="C130" s="16" t="n">
         <v>0.415</v>
       </c>
-      <c r="D130" s="13" t="n">
+      <c r="D130" s="16" t="n">
         <v>0.355</v>
       </c>
-      <c r="E130" s="13" t="n">
+      <c r="E130" s="16" t="n">
         <v>0.125</v>
       </c>
-      <c r="F130" s="13" t="n">
+      <c r="F130" s="16" t="n">
         <v>0.105</v>
       </c>
       <c r="G130" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H130" s="17"/>
-      <c r="L130" s="8"/>
+      <c r="H130" s="19"/>
+      <c r="I130" s="12"/>
+      <c r="J130" s="13"/>
+      <c r="K130" s="14"/>
+      <c r="L130" s="14"/>
+      <c r="M130" s="14"/>
+      <c r="N130" s="14"/>
     </row>
     <row r="131" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="12" t="n">
+      <c r="A131" s="15" t="n">
         <v>42141</v>
       </c>
       <c r="B131" s="9" t="s">
@@ -4984,11 +5655,16 @@
       <c r="G131" s="8" t="n">
         <v>1100</v>
       </c>
-      <c r="H131" s="17"/>
-      <c r="L131" s="8"/>
+      <c r="H131" s="19"/>
+      <c r="I131" s="12"/>
+      <c r="J131" s="13"/>
+      <c r="K131" s="14"/>
+      <c r="L131" s="14"/>
+      <c r="M131" s="14"/>
+      <c r="N131" s="14"/>
     </row>
     <row r="132" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="12" t="n">
+      <c r="A132" s="15" t="n">
         <v>42141</v>
       </c>
       <c r="B132" s="9" t="s">
@@ -5009,33 +5685,43 @@
       <c r="G132" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H132" s="17"/>
-      <c r="L132" s="8"/>
+      <c r="H132" s="19"/>
+      <c r="I132" s="12"/>
+      <c r="J132" s="13"/>
+      <c r="K132" s="14"/>
+      <c r="L132" s="14"/>
+      <c r="M132" s="14"/>
+      <c r="N132" s="14"/>
     </row>
     <row r="133" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="12" t="n">
+      <c r="A133" s="15" t="n">
         <v>42137</v>
       </c>
       <c r="B133" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="C133" s="13" t="n">
+      <c r="C133" s="16" t="n">
         <v>0.411</v>
       </c>
-      <c r="D133" s="13" t="n">
+      <c r="D133" s="16" t="n">
         <v>0.383</v>
       </c>
-      <c r="E133" s="13" t="n">
+      <c r="E133" s="16" t="n">
         <v>0.121</v>
       </c>
-      <c r="F133" s="13" t="n">
+      <c r="F133" s="16" t="n">
         <v>0.086</v>
       </c>
       <c r="G133" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H133" s="17"/>
-      <c r="L133" s="8"/>
+      <c r="H133" s="19"/>
+      <c r="I133" s="12"/>
+      <c r="J133" s="13"/>
+      <c r="K133" s="14"/>
+      <c r="L133" s="14"/>
+      <c r="M133" s="14"/>
+      <c r="N133" s="14"/>
     </row>
     <row r="134" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
@@ -5059,11 +5745,16 @@
       <c r="G134" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H134" s="17"/>
-      <c r="L134" s="8"/>
+      <c r="H134" s="19"/>
+      <c r="I134" s="12"/>
+      <c r="J134" s="13"/>
+      <c r="K134" s="14"/>
+      <c r="L134" s="14"/>
+      <c r="M134" s="14"/>
+      <c r="N134" s="14"/>
     </row>
     <row r="135" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="12" t="n">
+      <c r="A135" s="15" t="n">
         <v>42128</v>
       </c>
       <c r="B135" s="9" t="s">
@@ -5084,11 +5775,16 @@
       <c r="G135" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H135" s="17"/>
-      <c r="L135" s="8"/>
+      <c r="H135" s="19"/>
+      <c r="I135" s="27"/>
+      <c r="J135" s="13"/>
+      <c r="K135" s="14"/>
+      <c r="L135" s="14"/>
+      <c r="M135" s="14"/>
+      <c r="N135" s="14"/>
     </row>
     <row r="136" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="12" t="n">
+      <c r="A136" s="15" t="n">
         <v>42128</v>
       </c>
       <c r="B136" s="9" t="s">
@@ -5097,10 +5793,10 @@
       <c r="C136" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="D136" s="13" t="n">
+      <c r="D136" s="16" t="n">
         <v>0.375</v>
       </c>
-      <c r="E136" s="13" t="n">
+      <c r="E136" s="16" t="n">
         <v>0.115</v>
       </c>
       <c r="F136" s="10" t="n">
@@ -5109,14 +5805,19 @@
       <c r="G136" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H136" s="17"/>
-      <c r="L136" s="8"/>
+      <c r="H136" s="19"/>
+      <c r="I136" s="12"/>
+      <c r="J136" s="13"/>
+      <c r="K136" s="14"/>
+      <c r="L136" s="14"/>
+      <c r="M136" s="14"/>
+      <c r="N136" s="14"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="12" t="n">
+      <c r="A137" s="15" t="n">
         <v>42122</v>
       </c>
-      <c r="B137" s="18" t="s">
+      <c r="B137" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C137" s="10" t="n">
@@ -5134,14 +5835,19 @@
       <c r="G137" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H137" s="20"/>
-      <c r="L137" s="8"/>
+      <c r="H137" s="22"/>
+      <c r="I137" s="12"/>
+      <c r="J137" s="13"/>
+      <c r="K137" s="14"/>
+      <c r="L137" s="14"/>
+      <c r="M137" s="14"/>
+      <c r="N137" s="14"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="12" t="n">
+      <c r="A138" s="15" t="n">
         <v>42115</v>
       </c>
-      <c r="B138" s="18" t="s">
+      <c r="B138" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C138" s="10" t="n">
@@ -5159,8 +5865,13 @@
       <c r="G138" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H138" s="17"/>
-      <c r="L138" s="8"/>
+      <c r="H138" s="19"/>
+      <c r="I138" s="12"/>
+      <c r="J138" s="13"/>
+      <c r="K138" s="14"/>
+      <c r="L138" s="14"/>
+      <c r="M138" s="14"/>
+      <c r="N138" s="14"/>
     </row>
     <row r="139" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
@@ -5169,7 +5880,7 @@
       <c r="B139" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="C139" s="13" t="n">
+      <c r="C139" s="16" t="n">
         <v>0.385</v>
       </c>
       <c r="D139" s="10" t="n">
@@ -5184,14 +5895,19 @@
       <c r="G139" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H139" s="17"/>
-      <c r="L139" s="8"/>
+      <c r="H139" s="19"/>
+      <c r="I139" s="12"/>
+      <c r="J139" s="13"/>
+      <c r="K139" s="14"/>
+      <c r="L139" s="14"/>
+      <c r="M139" s="14"/>
+      <c r="N139" s="14"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="12" t="n">
+      <c r="A140" s="15" t="n">
         <v>42108</v>
       </c>
-      <c r="B140" s="18" t="s">
+      <c r="B140" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C140" s="10" t="n">
@@ -5209,8 +5925,13 @@
       <c r="G140" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H140" s="17"/>
-      <c r="L140" s="8"/>
+      <c r="H140" s="19"/>
+      <c r="I140" s="12"/>
+      <c r="J140" s="13"/>
+      <c r="K140" s="14"/>
+      <c r="L140" s="14"/>
+      <c r="M140" s="14"/>
+      <c r="N140" s="14"/>
     </row>
     <row r="141" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
@@ -5234,8 +5955,13 @@
       <c r="G141" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H141" s="17"/>
-      <c r="L141" s="8"/>
+      <c r="H141" s="19"/>
+      <c r="I141" s="12"/>
+      <c r="J141" s="13"/>
+      <c r="K141" s="14"/>
+      <c r="L141" s="14"/>
+      <c r="M141" s="14"/>
+      <c r="N141" s="14"/>
     </row>
     <row r="142" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
@@ -5259,8 +5985,13 @@
       <c r="G142" s="8" t="n">
         <v>1100</v>
       </c>
-      <c r="H142" s="17"/>
-      <c r="L142" s="8"/>
+      <c r="H142" s="19"/>
+      <c r="I142" s="12"/>
+      <c r="J142" s="13"/>
+      <c r="K142" s="14"/>
+      <c r="L142" s="14"/>
+      <c r="M142" s="14"/>
+      <c r="N142" s="14"/>
     </row>
     <row r="143" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
@@ -5269,13 +6000,13 @@
       <c r="B143" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="C143" s="13" t="n">
+      <c r="C143" s="16" t="n">
         <v>0.405</v>
       </c>
       <c r="D143" s="10" t="n">
         <v>0.36</v>
       </c>
-      <c r="E143" s="13" t="n">
+      <c r="E143" s="16" t="n">
         <v>0.125</v>
       </c>
       <c r="F143" s="10" t="n">
@@ -5284,33 +6015,43 @@
       <c r="G143" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H143" s="17"/>
-      <c r="L143" s="8"/>
+      <c r="H143" s="19"/>
+      <c r="I143" s="12"/>
+      <c r="J143" s="13"/>
+      <c r="K143" s="14"/>
+      <c r="L143" s="14"/>
+      <c r="M143" s="14"/>
+      <c r="N143" s="14"/>
     </row>
     <row r="144" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="12" t="n">
+      <c r="A144" s="15" t="n">
         <v>42092</v>
       </c>
       <c r="B144" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="C144" s="13" t="n">
+      <c r="C144" s="16" t="n">
         <v>0.396</v>
       </c>
-      <c r="D144" s="13" t="n">
+      <c r="D144" s="16" t="n">
         <v>0.405</v>
       </c>
-      <c r="E144" s="13" t="n">
+      <c r="E144" s="16" t="n">
         <v>0.115</v>
       </c>
-      <c r="F144" s="13" t="n">
+      <c r="F144" s="16" t="n">
         <v>0.085</v>
       </c>
       <c r="G144" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H144" s="17"/>
-      <c r="L144" s="8"/>
+      <c r="H144" s="19"/>
+      <c r="I144" s="12"/>
+      <c r="J144" s="13"/>
+      <c r="K144" s="14"/>
+      <c r="L144" s="14"/>
+      <c r="M144" s="14"/>
+      <c r="N144" s="14"/>
     </row>
     <row r="145" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
@@ -5334,8 +6075,13 @@
       <c r="G145" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H145" s="17"/>
-      <c r="L145" s="8"/>
+      <c r="H145" s="19"/>
+      <c r="I145" s="12"/>
+      <c r="J145" s="13"/>
+      <c r="K145" s="14"/>
+      <c r="L145" s="14"/>
+      <c r="M145" s="14"/>
+      <c r="N145" s="14"/>
     </row>
     <row r="146" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
@@ -5359,14 +6105,19 @@
       <c r="G146" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H146" s="17"/>
-      <c r="L146" s="8"/>
+      <c r="H146" s="19"/>
+      <c r="I146" s="12"/>
+      <c r="J146" s="13"/>
+      <c r="K146" s="14"/>
+      <c r="L146" s="14"/>
+      <c r="M146" s="14"/>
+      <c r="N146" s="14"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="12" t="n">
+      <c r="A147" s="15" t="n">
         <v>42080</v>
       </c>
-      <c r="B147" s="18" t="s">
+      <c r="B147" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C147" s="10" t="n">
@@ -5384,11 +6135,16 @@
       <c r="G147" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H147" s="17"/>
-      <c r="L147" s="8"/>
+      <c r="H147" s="19"/>
+      <c r="I147" s="12"/>
+      <c r="J147" s="13"/>
+      <c r="K147" s="14"/>
+      <c r="L147" s="14"/>
+      <c r="M147" s="14"/>
+      <c r="N147" s="14"/>
     </row>
     <row r="148" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="12" t="n">
+      <c r="A148" s="15" t="n">
         <v>42073</v>
       </c>
       <c r="B148" s="9" t="s">
@@ -5409,8 +6165,13 @@
       <c r="G148" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H148" s="17"/>
-      <c r="L148" s="8"/>
+      <c r="H148" s="19"/>
+      <c r="I148" s="12"/>
+      <c r="J148" s="13"/>
+      <c r="K148" s="14"/>
+      <c r="L148" s="14"/>
+      <c r="M148" s="14"/>
+      <c r="N148" s="14"/>
     </row>
     <row r="149" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
@@ -5434,8 +6195,13 @@
       <c r="G149" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H149" s="17"/>
-      <c r="L149" s="8"/>
+      <c r="H149" s="19"/>
+      <c r="I149" s="12"/>
+      <c r="J149" s="13"/>
+      <c r="K149" s="14"/>
+      <c r="L149" s="14"/>
+      <c r="M149" s="14"/>
+      <c r="N149" s="14"/>
     </row>
     <row r="150" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
@@ -5450,23 +6216,28 @@
       <c r="D150" s="10" t="n">
         <v>0.38</v>
       </c>
-      <c r="E150" s="13" t="n">
+      <c r="E150" s="16" t="n">
         <v>0.125</v>
       </c>
-      <c r="F150" s="13" t="n">
+      <c r="F150" s="16" t="n">
         <v>0.115</v>
       </c>
       <c r="G150" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H150" s="17"/>
-      <c r="L150" s="8"/>
+      <c r="H150" s="19"/>
+      <c r="I150" s="12"/>
+      <c r="J150" s="13"/>
+      <c r="K150" s="14"/>
+      <c r="L150" s="14"/>
+      <c r="M150" s="14"/>
+      <c r="N150" s="14"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B151" s="18" t="s">
+      <c r="B151" s="20" t="s">
         <v>244</v>
       </c>
       <c r="C151" s="10" t="n">
@@ -5484,14 +6255,19 @@
       <c r="G151" s="8" t="n">
         <v>1100</v>
       </c>
-      <c r="H151" s="20"/>
-      <c r="L151" s="8"/>
+      <c r="H151" s="22"/>
+      <c r="I151" s="12"/>
+      <c r="J151" s="13"/>
+      <c r="K151" s="14"/>
+      <c r="L151" s="14"/>
+      <c r="M151" s="14"/>
+      <c r="N151" s="14"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B152" s="18" t="s">
+      <c r="B152" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C152" s="10" t="n">
@@ -5509,14 +6285,19 @@
       <c r="G152" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H152" s="17"/>
-      <c r="L152" s="8"/>
+      <c r="H152" s="19"/>
+      <c r="I152" s="12"/>
+      <c r="J152" s="13"/>
+      <c r="K152" s="14"/>
+      <c r="L152" s="14"/>
+      <c r="M152" s="14"/>
+      <c r="N152" s="14"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B153" s="18" t="s">
+      <c r="B153" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C153" s="10" t="n">
@@ -5534,14 +6315,19 @@
       <c r="G153" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H153" s="17"/>
-      <c r="L153" s="8"/>
+      <c r="H153" s="19"/>
+      <c r="I153" s="12"/>
+      <c r="J153" s="13"/>
+      <c r="K153" s="14"/>
+      <c r="L153" s="14"/>
+      <c r="M153" s="14"/>
+      <c r="N153" s="14"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B154" s="18" t="s">
+      <c r="B154" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C154" s="10" t="n">
@@ -5559,14 +6345,19 @@
       <c r="G154" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H154" s="17"/>
-      <c r="L154" s="8"/>
+      <c r="H154" s="19"/>
+      <c r="I154" s="12"/>
+      <c r="J154" s="13"/>
+      <c r="K154" s="14"/>
+      <c r="L154" s="14"/>
+      <c r="M154" s="14"/>
+      <c r="N154" s="14"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B155" s="18" t="s">
+      <c r="B155" s="20" t="s">
         <v>249</v>
       </c>
       <c r="C155" s="10" t="n">
@@ -5584,39 +6375,49 @@
       <c r="G155" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H155" s="17"/>
-      <c r="L155" s="8"/>
+      <c r="H155" s="19"/>
+      <c r="I155" s="12"/>
+      <c r="J155" s="13"/>
+      <c r="K155" s="14"/>
+      <c r="L155" s="14"/>
+      <c r="M155" s="14"/>
+      <c r="N155" s="14"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="12" t="n">
+      <c r="A156" s="15" t="n">
         <v>42040</v>
       </c>
-      <c r="B156" s="18" t="s">
+      <c r="B156" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="C156" s="13" t="n">
+      <c r="C156" s="16" t="n">
         <v>0.384</v>
       </c>
-      <c r="D156" s="13" t="n">
+      <c r="D156" s="16" t="n">
         <v>0.414</v>
       </c>
-      <c r="E156" s="13" t="n">
+      <c r="E156" s="16" t="n">
         <v>0.112</v>
       </c>
-      <c r="F156" s="13" t="n">
+      <c r="F156" s="16" t="n">
         <v>0.089</v>
       </c>
       <c r="G156" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H156" s="20"/>
-      <c r="L156" s="8"/>
+      <c r="H156" s="22"/>
+      <c r="I156" s="12"/>
+      <c r="J156" s="13"/>
+      <c r="K156" s="14"/>
+      <c r="L156" s="14"/>
+      <c r="M156" s="14"/>
+      <c r="N156" s="14"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B157" s="18" t="s">
+      <c r="B157" s="20" t="s">
         <v>252</v>
       </c>
       <c r="C157" s="10" t="n">
@@ -5634,14 +6435,19 @@
       <c r="G157" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H157" s="17"/>
-      <c r="L157" s="8"/>
+      <c r="H157" s="19"/>
+      <c r="I157" s="12"/>
+      <c r="J157" s="13"/>
+      <c r="K157" s="14"/>
+      <c r="L157" s="14"/>
+      <c r="M157" s="14"/>
+      <c r="N157" s="14"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B158" s="18" t="s">
+      <c r="B158" s="20" t="s">
         <v>252</v>
       </c>
       <c r="C158" s="10" t="n">
@@ -5659,39 +6465,49 @@
       <c r="G158" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H158" s="17"/>
-      <c r="L158" s="8"/>
+      <c r="H158" s="19"/>
+      <c r="I158" s="12"/>
+      <c r="J158" s="13"/>
+      <c r="K158" s="14"/>
+      <c r="L158" s="14"/>
+      <c r="M158" s="14"/>
+      <c r="N158" s="14"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="12" t="n">
+      <c r="A159" s="15" t="n">
         <v>42031</v>
       </c>
-      <c r="B159" s="18" t="s">
+      <c r="B159" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="C159" s="13" t="n">
+      <c r="C159" s="16" t="n">
         <v>0.397</v>
       </c>
-      <c r="D159" s="13" t="n">
+      <c r="D159" s="16" t="n">
         <v>0.402</v>
       </c>
-      <c r="E159" s="13" t="n">
+      <c r="E159" s="16" t="n">
         <v>0.113</v>
       </c>
-      <c r="F159" s="13" t="n">
+      <c r="F159" s="16" t="n">
         <v>0.088</v>
       </c>
       <c r="G159" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H159" s="17"/>
-      <c r="L159" s="8"/>
+      <c r="H159" s="19"/>
+      <c r="I159" s="12"/>
+      <c r="J159" s="13"/>
+      <c r="K159" s="14"/>
+      <c r="L159" s="14"/>
+      <c r="M159" s="14"/>
+      <c r="N159" s="14"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="12" t="n">
+      <c r="A160" s="15" t="n">
         <v>42031</v>
       </c>
-      <c r="B160" s="18" t="s">
+      <c r="B160" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C160" s="10" t="n">
@@ -5709,14 +6525,19 @@
       <c r="G160" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H160" s="17"/>
-      <c r="L160" s="8"/>
+      <c r="H160" s="19"/>
+      <c r="I160" s="12"/>
+      <c r="J160" s="13"/>
+      <c r="K160" s="14"/>
+      <c r="L160" s="14"/>
+      <c r="M160" s="14"/>
+      <c r="N160" s="14"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="12" t="n">
+      <c r="A161" s="15" t="n">
         <v>42024</v>
       </c>
-      <c r="B161" s="18" t="s">
+      <c r="B161" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C161" s="10" t="n">
@@ -5734,14 +6555,19 @@
       <c r="G161" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H161" s="17"/>
-      <c r="L161" s="8"/>
+      <c r="H161" s="19"/>
+      <c r="I161" s="12"/>
+      <c r="J161" s="13"/>
+      <c r="K161" s="14"/>
+      <c r="L161" s="14"/>
+      <c r="M161" s="14"/>
+      <c r="N161" s="14"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="12" t="n">
+      <c r="A162" s="15" t="n">
         <v>42017</v>
       </c>
-      <c r="B162" s="18" t="s">
+      <c r="B162" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C162" s="10" t="n">
@@ -5759,45 +6585,55 @@
       <c r="G162" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H162" s="17"/>
-      <c r="L162" s="8"/>
+      <c r="H162" s="19"/>
+      <c r="I162" s="12"/>
+      <c r="J162" s="13"/>
+      <c r="K162" s="14"/>
+      <c r="L162" s="14"/>
+      <c r="M162" s="14"/>
+      <c r="N162" s="14"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="12" t="n">
+      <c r="A163" s="15" t="n">
         <v>42016</v>
       </c>
-      <c r="B163" s="18" t="s">
+      <c r="B163" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="C163" s="13" t="n">
+      <c r="C163" s="16" t="n">
         <v>0.385</v>
       </c>
-      <c r="D163" s="13" t="n">
+      <c r="D163" s="16" t="n">
         <v>0.385</v>
       </c>
-      <c r="E163" s="13" t="n">
+      <c r="E163" s="16" t="n">
         <v>0.095</v>
       </c>
-      <c r="F163" s="13" t="n">
+      <c r="F163" s="16" t="n">
         <v>0.135</v>
       </c>
       <c r="G163" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H163" s="17"/>
-      <c r="L163" s="8"/>
+      <c r="H163" s="19"/>
+      <c r="I163" s="12"/>
+      <c r="J163" s="13"/>
+      <c r="K163" s="14"/>
+      <c r="L163" s="14"/>
+      <c r="M163" s="14"/>
+      <c r="N163" s="14"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B164" s="18" t="s">
+      <c r="B164" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="C164" s="13" t="n">
+      <c r="C164" s="16" t="n">
         <v>0.375</v>
       </c>
-      <c r="D164" s="13" t="n">
+      <c r="D164" s="16" t="n">
         <v>0.395</v>
       </c>
       <c r="E164" s="10" t="n">
@@ -5809,14 +6645,19 @@
       <c r="G164" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H164" s="20"/>
-      <c r="L164" s="8"/>
+      <c r="H164" s="22"/>
+      <c r="I164" s="12"/>
+      <c r="J164" s="13"/>
+      <c r="K164" s="14"/>
+      <c r="L164" s="14"/>
+      <c r="M164" s="14"/>
+      <c r="N164" s="14"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="12" t="n">
+      <c r="A165" s="15" t="n">
         <v>41989</v>
       </c>
-      <c r="B165" s="18" t="s">
+      <c r="B165" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C165" s="10" t="n">
@@ -5834,14 +6675,19 @@
       <c r="G165" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H165" s="20"/>
-      <c r="L165" s="8"/>
+      <c r="H165" s="22"/>
+      <c r="I165" s="12"/>
+      <c r="J165" s="13"/>
+      <c r="K165" s="14"/>
+      <c r="L165" s="14"/>
+      <c r="M165" s="14"/>
+      <c r="N165" s="14"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B166" s="18" t="s">
+      <c r="B166" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C166" s="10" t="n">
@@ -5859,14 +6705,19 @@
       <c r="G166" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H166" s="17"/>
-      <c r="L166" s="8"/>
+      <c r="H166" s="19"/>
+      <c r="I166" s="12"/>
+      <c r="J166" s="13"/>
+      <c r="K166" s="14"/>
+      <c r="L166" s="14"/>
+      <c r="M166" s="14"/>
+      <c r="N166" s="14"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B167" s="18" t="s">
+      <c r="B167" s="20" t="s">
         <v>249</v>
       </c>
       <c r="C167" s="10" t="n">
@@ -5875,23 +6726,28 @@
       <c r="D167" s="10" t="n">
         <v>0.41</v>
       </c>
-      <c r="E167" s="13" t="n">
+      <c r="E167" s="16" t="n">
         <v>0.115</v>
       </c>
-      <c r="F167" s="13" t="n">
+      <c r="F167" s="16" t="n">
         <v>0.125</v>
       </c>
       <c r="G167" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H167" s="17"/>
-      <c r="L167" s="8"/>
+      <c r="H167" s="19"/>
+      <c r="I167" s="12"/>
+      <c r="J167" s="13"/>
+      <c r="K167" s="14"/>
+      <c r="L167" s="14"/>
+      <c r="M167" s="14"/>
+      <c r="N167" s="14"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B168" s="18" t="s">
+      <c r="B168" s="20" t="s">
         <v>244</v>
       </c>
       <c r="C168" s="10" t="n">
@@ -5909,14 +6765,19 @@
       <c r="G168" s="8" t="n">
         <v>1100</v>
       </c>
-      <c r="H168" s="20"/>
-      <c r="L168" s="8"/>
+      <c r="H168" s="22"/>
+      <c r="I168" s="12"/>
+      <c r="J168" s="13"/>
+      <c r="K168" s="14"/>
+      <c r="L168" s="14"/>
+      <c r="M168" s="14"/>
+      <c r="N168" s="14"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B169" s="18" t="s">
+      <c r="B169" s="20" t="s">
         <v>252</v>
       </c>
       <c r="C169" s="10" t="n">
@@ -5934,14 +6795,19 @@
       <c r="G169" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H169" s="17"/>
-      <c r="L169" s="8"/>
+      <c r="H169" s="19"/>
+      <c r="I169" s="12"/>
+      <c r="J169" s="13"/>
+      <c r="K169" s="14"/>
+      <c r="L169" s="14"/>
+      <c r="M169" s="14"/>
+      <c r="N169" s="14"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="12" t="n">
+      <c r="A170" s="15" t="n">
         <v>41975</v>
       </c>
-      <c r="B170" s="18" t="s">
+      <c r="B170" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C170" s="10" t="n">
@@ -5959,14 +6825,19 @@
       <c r="G170" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H170" s="17"/>
-      <c r="L170" s="8"/>
+      <c r="H170" s="19"/>
+      <c r="I170" s="12"/>
+      <c r="J170" s="13"/>
+      <c r="K170" s="14"/>
+      <c r="L170" s="14"/>
+      <c r="M170" s="14"/>
+      <c r="N170" s="14"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B171" s="18" t="s">
+      <c r="B171" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C171" s="10" t="n">
@@ -5984,39 +6855,49 @@
       <c r="G171" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H171" s="17"/>
-      <c r="L171" s="8"/>
+      <c r="H171" s="19"/>
+      <c r="I171" s="12"/>
+      <c r="J171" s="13"/>
+      <c r="K171" s="14"/>
+      <c r="L171" s="14"/>
+      <c r="M171" s="14"/>
+      <c r="N171" s="14"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B172" s="18" t="s">
+      <c r="B172" s="20" t="s">
         <v>249</v>
       </c>
       <c r="C172" s="10" t="n">
         <v>0.37</v>
       </c>
-      <c r="D172" s="13" t="n">
+      <c r="D172" s="16" t="n">
         <v>0.375</v>
       </c>
       <c r="E172" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="F172" s="13" t="n">
+      <c r="F172" s="16" t="n">
         <v>0.115</v>
       </c>
       <c r="G172" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H172" s="17"/>
-      <c r="L172" s="8"/>
+      <c r="H172" s="19"/>
+      <c r="I172" s="12"/>
+      <c r="J172" s="13"/>
+      <c r="K172" s="14"/>
+      <c r="L172" s="14"/>
+      <c r="M172" s="14"/>
+      <c r="N172" s="14"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="12" t="n">
+      <c r="A173" s="15" t="n">
         <v>41968</v>
       </c>
-      <c r="B173" s="18" t="s">
+      <c r="B173" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C173" s="10" t="n">
@@ -6034,39 +6915,49 @@
       <c r="G173" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H173" s="20"/>
-      <c r="L173" s="8"/>
+      <c r="H173" s="22"/>
+      <c r="I173" s="12"/>
+      <c r="J173" s="13"/>
+      <c r="K173" s="14"/>
+      <c r="L173" s="14"/>
+      <c r="M173" s="14"/>
+      <c r="N173" s="14"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="12" t="n">
+      <c r="A174" s="15" t="n">
         <v>41964</v>
       </c>
-      <c r="B174" s="18" t="s">
+      <c r="B174" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="C174" s="13" t="n">
+      <c r="C174" s="16" t="n">
         <v>0.402</v>
       </c>
-      <c r="D174" s="13" t="n">
+      <c r="D174" s="16" t="n">
         <v>0.387</v>
       </c>
-      <c r="E174" s="13" t="n">
+      <c r="E174" s="16" t="n">
         <v>0.111</v>
       </c>
-      <c r="F174" s="13" t="n">
+      <c r="F174" s="16" t="n">
         <v>0.099</v>
       </c>
       <c r="G174" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H174" s="17"/>
-      <c r="L174" s="8"/>
+      <c r="H174" s="19"/>
+      <c r="I174" s="12"/>
+      <c r="J174" s="13"/>
+      <c r="K174" s="14"/>
+      <c r="L174" s="14"/>
+      <c r="M174" s="14"/>
+      <c r="N174" s="14"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="12" t="n">
+      <c r="A175" s="15" t="n">
         <v>41961</v>
       </c>
-      <c r="B175" s="18" t="s">
+      <c r="B175" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C175" s="10" t="n">
@@ -6084,14 +6975,19 @@
       <c r="G175" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H175" s="17"/>
-      <c r="L175" s="8"/>
+      <c r="H175" s="19"/>
+      <c r="I175" s="12"/>
+      <c r="J175" s="13"/>
+      <c r="K175" s="14"/>
+      <c r="L175" s="14"/>
+      <c r="M175" s="14"/>
+      <c r="N175" s="14"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="12" t="n">
+      <c r="A176" s="15" t="n">
         <v>41960</v>
       </c>
-      <c r="B176" s="18" t="s">
+      <c r="B176" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C176" s="10" t="n">
@@ -6109,39 +7005,49 @@
       <c r="G176" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H176" s="17"/>
-      <c r="L176" s="8"/>
+      <c r="H176" s="19"/>
+      <c r="I176" s="12"/>
+      <c r="J176" s="13"/>
+      <c r="K176" s="14"/>
+      <c r="L176" s="14"/>
+      <c r="M176" s="14"/>
+      <c r="N176" s="14"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="12" t="n">
+      <c r="A177" s="15" t="n">
         <v>41960</v>
       </c>
-      <c r="B177" s="18" t="s">
+      <c r="B177" s="20" t="s">
         <v>249</v>
       </c>
       <c r="C177" s="10" t="n">
         <v>0.38</v>
       </c>
-      <c r="D177" s="13" t="n">
+      <c r="D177" s="16" t="n">
         <v>0.385</v>
       </c>
       <c r="E177" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="F177" s="13" t="n">
+      <c r="F177" s="16" t="n">
         <v>0.115</v>
       </c>
       <c r="G177" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H177" s="17"/>
-      <c r="L177" s="8"/>
+      <c r="H177" s="19"/>
+      <c r="I177" s="12"/>
+      <c r="J177" s="13"/>
+      <c r="K177" s="14"/>
+      <c r="L177" s="14"/>
+      <c r="M177" s="14"/>
+      <c r="N177" s="14"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="12" t="n">
+      <c r="A178" s="15" t="n">
         <v>41954</v>
       </c>
-      <c r="B178" s="18" t="s">
+      <c r="B178" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C178" s="10" t="n">
@@ -6159,14 +7065,19 @@
       <c r="G178" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H178" s="20"/>
-      <c r="L178" s="8"/>
+      <c r="H178" s="22"/>
+      <c r="I178" s="12"/>
+      <c r="J178" s="13"/>
+      <c r="K178" s="14"/>
+      <c r="L178" s="14"/>
+      <c r="M178" s="14"/>
+      <c r="N178" s="14"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="12" t="n">
+      <c r="A179" s="15" t="n">
         <v>41947</v>
       </c>
-      <c r="B179" s="18" t="s">
+      <c r="B179" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C179" s="10" t="n">
@@ -6184,14 +7095,19 @@
       <c r="G179" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H179" s="17"/>
-      <c r="L179" s="8"/>
+      <c r="H179" s="19"/>
+      <c r="I179" s="12"/>
+      <c r="J179" s="13"/>
+      <c r="K179" s="14"/>
+      <c r="L179" s="14"/>
+      <c r="M179" s="14"/>
+      <c r="N179" s="14"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="12" t="n">
+      <c r="A180" s="15" t="n">
         <v>41947</v>
       </c>
-      <c r="B180" s="18" t="s">
+      <c r="B180" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C180" s="10" t="n">
@@ -6209,39 +7125,49 @@
       <c r="G180" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H180" s="17"/>
-      <c r="L180" s="8"/>
+      <c r="H180" s="19"/>
+      <c r="I180" s="12"/>
+      <c r="J180" s="13"/>
+      <c r="K180" s="14"/>
+      <c r="L180" s="14"/>
+      <c r="M180" s="14"/>
+      <c r="N180" s="14"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B181" s="18" t="s">
+      <c r="B181" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="C181" s="13" t="n">
+      <c r="C181" s="16" t="n">
         <v>0.385</v>
       </c>
-      <c r="D181" s="13" t="n">
+      <c r="D181" s="16" t="n">
         <v>0.375</v>
       </c>
-      <c r="E181" s="13" t="n">
+      <c r="E181" s="16" t="n">
         <v>0.125</v>
       </c>
-      <c r="F181" s="13" t="n">
+      <c r="F181" s="16" t="n">
         <v>0.115</v>
       </c>
       <c r="G181" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H181" s="17"/>
-      <c r="L181" s="8"/>
+      <c r="H181" s="19"/>
+      <c r="I181" s="12"/>
+      <c r="J181" s="13"/>
+      <c r="K181" s="14"/>
+      <c r="L181" s="14"/>
+      <c r="M181" s="14"/>
+      <c r="N181" s="14"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B182" s="18" t="s">
+      <c r="B182" s="20" t="s">
         <v>244</v>
       </c>
       <c r="C182" s="10" t="n">
@@ -6259,14 +7185,19 @@
       <c r="G182" s="8" t="n">
         <v>1100</v>
       </c>
-      <c r="H182" s="20"/>
-      <c r="L182" s="8"/>
+      <c r="H182" s="22"/>
+      <c r="I182" s="12"/>
+      <c r="J182" s="13"/>
+      <c r="K182" s="14"/>
+      <c r="L182" s="14"/>
+      <c r="M182" s="14"/>
+      <c r="N182" s="14"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="12" t="n">
+      <c r="A183" s="15" t="n">
         <v>41940</v>
       </c>
-      <c r="B183" s="18" t="s">
+      <c r="B183" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C183" s="10" t="n">
@@ -6284,39 +7215,49 @@
       <c r="G183" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H183" s="17"/>
-      <c r="L183" s="8"/>
+      <c r="H183" s="19"/>
+      <c r="I183" s="12"/>
+      <c r="J183" s="13"/>
+      <c r="K183" s="14"/>
+      <c r="L183" s="14"/>
+      <c r="M183" s="14"/>
+      <c r="N183" s="14"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="12" t="n">
+      <c r="A184" s="15" t="n">
         <v>41935</v>
       </c>
-      <c r="B184" s="18" t="s">
+      <c r="B184" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="C184" s="13" t="n">
+      <c r="C184" s="16" t="n">
         <v>0.401</v>
       </c>
-      <c r="D184" s="13" t="n">
+      <c r="D184" s="16" t="n">
         <v>0.375</v>
       </c>
-      <c r="E184" s="13" t="n">
+      <c r="E184" s="16" t="n">
         <v>0.115</v>
       </c>
-      <c r="F184" s="13" t="n">
+      <c r="F184" s="16" t="n">
         <v>0.109</v>
       </c>
       <c r="G184" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H184" s="17"/>
-      <c r="L184" s="8"/>
+      <c r="H184" s="19"/>
+      <c r="I184" s="12"/>
+      <c r="J184" s="13"/>
+      <c r="K184" s="14"/>
+      <c r="L184" s="14"/>
+      <c r="M184" s="14"/>
+      <c r="N184" s="14"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="12" t="n">
+      <c r="A185" s="15" t="n">
         <v>41933</v>
       </c>
-      <c r="B185" s="18" t="s">
+      <c r="B185" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C185" s="10" t="n">
@@ -6334,14 +7275,19 @@
       <c r="G185" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H185" s="17"/>
-      <c r="L185" s="8"/>
+      <c r="H185" s="19"/>
+      <c r="I185" s="12"/>
+      <c r="J185" s="13"/>
+      <c r="K185" s="14"/>
+      <c r="L185" s="14"/>
+      <c r="M185" s="14"/>
+      <c r="N185" s="14"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="12" t="n">
+      <c r="A186" s="15" t="n">
         <v>41933</v>
       </c>
-      <c r="B186" s="18" t="s">
+      <c r="B186" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C186" s="10" t="n">
@@ -6359,20 +7305,25 @@
       <c r="G186" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H186" s="17"/>
-      <c r="L186" s="8"/>
+      <c r="H186" s="19"/>
+      <c r="I186" s="12"/>
+      <c r="J186" s="13"/>
+      <c r="K186" s="14"/>
+      <c r="L186" s="14"/>
+      <c r="M186" s="14"/>
+      <c r="N186" s="14"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="12" t="n">
+      <c r="A187" s="15" t="n">
         <v>41932</v>
       </c>
-      <c r="B187" s="18" t="s">
+      <c r="B187" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="C187" s="13" t="n">
+      <c r="C187" s="16" t="n">
         <v>0.395</v>
       </c>
-      <c r="D187" s="13" t="n">
+      <c r="D187" s="16" t="n">
         <v>0.355</v>
       </c>
       <c r="E187" s="10" t="n">
@@ -6384,14 +7335,19 @@
       <c r="G187" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H187" s="17"/>
-      <c r="L187" s="8"/>
+      <c r="H187" s="19"/>
+      <c r="I187" s="12"/>
+      <c r="J187" s="13"/>
+      <c r="K187" s="14"/>
+      <c r="L187" s="14"/>
+      <c r="M187" s="14"/>
+      <c r="N187" s="14"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="12" t="n">
+      <c r="A188" s="15" t="n">
         <v>41926</v>
       </c>
-      <c r="B188" s="18" t="s">
+      <c r="B188" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C188" s="10" t="n">
@@ -6409,14 +7365,19 @@
       <c r="G188" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H188" s="17"/>
-      <c r="L188" s="8"/>
+      <c r="H188" s="19"/>
+      <c r="I188" s="12"/>
+      <c r="J188" s="13"/>
+      <c r="K188" s="14"/>
+      <c r="L188" s="14"/>
+      <c r="M188" s="14"/>
+      <c r="N188" s="14"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="12" t="n">
+      <c r="A189" s="15" t="n">
         <v>41919</v>
       </c>
-      <c r="B189" s="18" t="s">
+      <c r="B189" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C189" s="10" t="n">
@@ -6434,14 +7395,19 @@
       <c r="G189" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H189" s="17"/>
-      <c r="L189" s="8"/>
+      <c r="H189" s="19"/>
+      <c r="I189" s="12"/>
+      <c r="J189" s="13"/>
+      <c r="K189" s="14"/>
+      <c r="L189" s="14"/>
+      <c r="M189" s="14"/>
+      <c r="N189" s="14"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B190" s="18" t="s">
+      <c r="B190" s="20" t="s">
         <v>249</v>
       </c>
       <c r="C190" s="10" t="n">
@@ -6459,14 +7425,19 @@
       <c r="G190" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H190" s="17"/>
-      <c r="L190" s="8"/>
+      <c r="H190" s="19"/>
+      <c r="I190" s="12"/>
+      <c r="J190" s="13"/>
+      <c r="K190" s="14"/>
+      <c r="L190" s="14"/>
+      <c r="M190" s="14"/>
+      <c r="N190" s="14"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B191" s="18" t="s">
+      <c r="B191" s="20" t="s">
         <v>252</v>
       </c>
       <c r="C191" s="10" t="n">
@@ -6484,14 +7455,19 @@
       <c r="G191" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H191" s="17"/>
-      <c r="L191" s="8"/>
+      <c r="H191" s="19"/>
+      <c r="I191" s="12"/>
+      <c r="J191" s="13"/>
+      <c r="K191" s="14"/>
+      <c r="L191" s="14"/>
+      <c r="M191" s="14"/>
+      <c r="N191" s="14"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="12" t="n">
+      <c r="A192" s="15" t="n">
         <v>41905</v>
       </c>
-      <c r="B192" s="18" t="s">
+      <c r="B192" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C192" s="10" t="n">
@@ -6509,20 +7485,25 @@
       <c r="G192" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H192" s="17"/>
-      <c r="L192" s="8"/>
+      <c r="H192" s="19"/>
+      <c r="I192" s="12"/>
+      <c r="J192" s="13"/>
+      <c r="K192" s="14"/>
+      <c r="L192" s="14"/>
+      <c r="M192" s="14"/>
+      <c r="N192" s="14"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B193" s="18" t="s">
+      <c r="B193" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="C193" s="13" t="n">
+      <c r="C193" s="16" t="n">
         <v>0.385</v>
       </c>
-      <c r="D193" s="13" t="n">
+      <c r="D193" s="16" t="n">
         <v>0.375</v>
       </c>
       <c r="E193" s="10" t="n">
@@ -6534,39 +7515,49 @@
       <c r="G193" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H193" s="17"/>
-      <c r="L193" s="8"/>
+      <c r="H193" s="19"/>
+      <c r="I193" s="12"/>
+      <c r="J193" s="13"/>
+      <c r="K193" s="14"/>
+      <c r="L193" s="14"/>
+      <c r="M193" s="14"/>
+      <c r="N193" s="14"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="12" t="n">
+      <c r="A194" s="15" t="n">
         <v>41900</v>
       </c>
-      <c r="B194" s="18" t="s">
+      <c r="B194" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="C194" s="13" t="n">
+      <c r="C194" s="16" t="n">
         <v>0.416</v>
       </c>
-      <c r="D194" s="13" t="n">
+      <c r="D194" s="16" t="n">
         <v>0.374</v>
       </c>
-      <c r="E194" s="13" t="n">
+      <c r="E194" s="16" t="n">
         <v>0.105</v>
       </c>
-      <c r="F194" s="13" t="n">
+      <c r="F194" s="16" t="n">
         <v>0.105</v>
       </c>
       <c r="G194" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H194" s="20"/>
-      <c r="L194" s="8"/>
+      <c r="H194" s="22"/>
+      <c r="I194" s="12"/>
+      <c r="J194" s="13"/>
+      <c r="K194" s="14"/>
+      <c r="L194" s="14"/>
+      <c r="M194" s="14"/>
+      <c r="N194" s="14"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B195" s="18" t="s">
+      <c r="B195" s="20" t="s">
         <v>249</v>
       </c>
       <c r="C195" s="10" t="n">
@@ -6575,23 +7566,28 @@
       <c r="D195" s="10" t="n">
         <v>0.37</v>
       </c>
-      <c r="E195" s="13" t="n">
+      <c r="E195" s="16" t="n">
         <v>0.105</v>
       </c>
-      <c r="F195" s="13" t="n">
+      <c r="F195" s="16" t="n">
         <v>0.145</v>
       </c>
       <c r="G195" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H195" s="17"/>
-      <c r="L195" s="8"/>
+      <c r="H195" s="19"/>
+      <c r="I195" s="12"/>
+      <c r="J195" s="13"/>
+      <c r="K195" s="14"/>
+      <c r="L195" s="14"/>
+      <c r="M195" s="14"/>
+      <c r="N195" s="14"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B196" s="18" t="s">
+      <c r="B196" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C196" s="10" t="n">
@@ -6609,14 +7605,19 @@
       <c r="G196" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H196" s="17"/>
-      <c r="L196" s="8"/>
+      <c r="H196" s="19"/>
+      <c r="I196" s="12"/>
+      <c r="J196" s="13"/>
+      <c r="K196" s="14"/>
+      <c r="L196" s="14"/>
+      <c r="M196" s="14"/>
+      <c r="N196" s="14"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B197" s="18" t="s">
+      <c r="B197" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C197" s="10" t="n">
@@ -6634,39 +7635,49 @@
       <c r="G197" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H197" s="17"/>
-      <c r="L197" s="8"/>
+      <c r="H197" s="19"/>
+      <c r="I197" s="12"/>
+      <c r="J197" s="13"/>
+      <c r="K197" s="14"/>
+      <c r="L197" s="14"/>
+      <c r="M197" s="14"/>
+      <c r="N197" s="14"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B198" s="18" t="s">
+      <c r="B198" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="C198" s="13" t="n">
+      <c r="C198" s="16" t="n">
         <v>0.375</v>
       </c>
-      <c r="D198" s="13" t="n">
+      <c r="D198" s="16" t="n">
         <v>0.385</v>
       </c>
-      <c r="E198" s="13" t="n">
+      <c r="E198" s="16" t="n">
         <v>0.105</v>
       </c>
-      <c r="F198" s="13" t="n">
+      <c r="F198" s="16" t="n">
         <v>0.135</v>
       </c>
       <c r="G198" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H198" s="17"/>
-      <c r="L198" s="8"/>
+      <c r="H198" s="19"/>
+      <c r="I198" s="12"/>
+      <c r="J198" s="13"/>
+      <c r="K198" s="14"/>
+      <c r="L198" s="14"/>
+      <c r="M198" s="14"/>
+      <c r="N198" s="14"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="12" t="n">
+      <c r="A199" s="15" t="n">
         <v>41870</v>
       </c>
-      <c r="B199" s="18" t="s">
+      <c r="B199" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C199" s="10" t="n">
@@ -6684,17 +7695,22 @@
       <c r="G199" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H199" s="20"/>
-      <c r="L199" s="8"/>
+      <c r="H199" s="22"/>
+      <c r="I199" s="12"/>
+      <c r="J199" s="13"/>
+      <c r="K199" s="14"/>
+      <c r="L199" s="14"/>
+      <c r="M199" s="14"/>
+      <c r="N199" s="14"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B200" s="18" t="s">
+      <c r="B200" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="C200" s="13" t="n">
+      <c r="C200" s="16" t="n">
         <v>0.375</v>
       </c>
       <c r="D200" s="10" t="n">
@@ -6703,20 +7719,25 @@
       <c r="E200" s="10" t="n">
         <v>0.11</v>
       </c>
-      <c r="F200" s="13" t="n">
+      <c r="F200" s="16" t="n">
         <v>0.135</v>
       </c>
       <c r="G200" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H200" s="17"/>
-      <c r="L200" s="8"/>
+      <c r="H200" s="19"/>
+      <c r="I200" s="12"/>
+      <c r="J200" s="13"/>
+      <c r="K200" s="14"/>
+      <c r="L200" s="14"/>
+      <c r="M200" s="14"/>
+      <c r="N200" s="14"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B201" s="18" t="s">
+      <c r="B201" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C201" s="10" t="n">
@@ -6734,14 +7755,19 @@
       <c r="G201" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H201" s="17"/>
-      <c r="L201" s="8"/>
+      <c r="H201" s="19"/>
+      <c r="I201" s="12"/>
+      <c r="J201" s="13"/>
+      <c r="K201" s="14"/>
+      <c r="L201" s="14"/>
+      <c r="M201" s="14"/>
+      <c r="N201" s="14"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B202" s="18" t="s">
+      <c r="B202" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C202" s="10" t="n">
@@ -6759,14 +7785,19 @@
       <c r="G202" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H202" s="17"/>
-      <c r="L202" s="8"/>
+      <c r="H202" s="19"/>
+      <c r="I202" s="12"/>
+      <c r="J202" s="13"/>
+      <c r="K202" s="14"/>
+      <c r="L202" s="14"/>
+      <c r="M202" s="14"/>
+      <c r="N202" s="14"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="B203" s="18" t="s">
+      <c r="B203" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C203" s="10" t="n">
@@ -6784,11 +7815,16 @@
       <c r="G203" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H203" s="17"/>
-      <c r="L203" s="8"/>
+      <c r="H203" s="19"/>
+      <c r="I203" s="12"/>
+      <c r="J203" s="13"/>
+      <c r="K203" s="14"/>
+      <c r="L203" s="14"/>
+      <c r="M203" s="14"/>
+      <c r="N203" s="14"/>
     </row>
     <row r="204" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="12" t="n">
+      <c r="A204" s="15" t="n">
         <v>41821</v>
       </c>
       <c r="B204" s="9" t="s">
@@ -6809,11 +7845,16 @@
       <c r="G204" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H204" s="17"/>
-      <c r="L204" s="8"/>
+      <c r="H204" s="19"/>
+      <c r="I204" s="12"/>
+      <c r="J204" s="13"/>
+      <c r="K204" s="14"/>
+      <c r="L204" s="14"/>
+      <c r="M204" s="14"/>
+      <c r="N204" s="14"/>
     </row>
     <row r="205" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="12" t="n">
+      <c r="A205" s="15" t="n">
         <v>41820</v>
       </c>
       <c r="B205" s="9" t="s">
@@ -6822,26 +7863,31 @@
       <c r="C205" s="10" t="n">
         <v>0.35</v>
       </c>
-      <c r="D205" s="13" t="n">
+      <c r="D205" s="16" t="n">
         <v>0.365</v>
       </c>
       <c r="E205" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="F205" s="13" t="n">
+      <c r="F205" s="16" t="n">
         <v>0.165</v>
       </c>
       <c r="G205" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H205" s="17"/>
-      <c r="L205" s="8"/>
+      <c r="H205" s="19"/>
+      <c r="I205" s="12"/>
+      <c r="J205" s="13"/>
+      <c r="K205" s="14"/>
+      <c r="L205" s="14"/>
+      <c r="M205" s="14"/>
+      <c r="N205" s="14"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B206" s="18" t="s">
+      <c r="B206" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C206" s="10" t="n">
@@ -6859,14 +7905,19 @@
       <c r="G206" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H206" s="20"/>
-      <c r="L206" s="8"/>
+      <c r="H206" s="22"/>
+      <c r="I206" s="12"/>
+      <c r="J206" s="13"/>
+      <c r="K206" s="14"/>
+      <c r="L206" s="14"/>
+      <c r="M206" s="14"/>
+      <c r="N206" s="14"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B207" s="18" t="s">
+      <c r="B207" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C207" s="10" t="n">
@@ -6884,14 +7935,19 @@
       <c r="G207" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H207" s="17"/>
-      <c r="L207" s="8"/>
+      <c r="H207" s="19"/>
+      <c r="I207" s="12"/>
+      <c r="J207" s="13"/>
+      <c r="K207" s="14"/>
+      <c r="L207" s="14"/>
+      <c r="M207" s="14"/>
+      <c r="N207" s="14"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B208" s="18" t="s">
+      <c r="B208" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C208" s="10" t="n">
@@ -6909,11 +7965,16 @@
       <c r="G208" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H208" s="17"/>
-      <c r="L208" s="8"/>
+      <c r="H208" s="19"/>
+      <c r="I208" s="12"/>
+      <c r="J208" s="13"/>
+      <c r="K208" s="14"/>
+      <c r="L208" s="14"/>
+      <c r="M208" s="14"/>
+      <c r="N208" s="14"/>
     </row>
     <row r="209" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="12" t="n">
+      <c r="A209" s="15" t="n">
         <v>41786</v>
       </c>
       <c r="B209" s="9" t="s">
@@ -6934,11 +7995,16 @@
       <c r="G209" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H209" s="17"/>
-      <c r="L209" s="8"/>
+      <c r="H209" s="19"/>
+      <c r="I209" s="12"/>
+      <c r="J209" s="13"/>
+      <c r="K209" s="14"/>
+      <c r="L209" s="14"/>
+      <c r="M209" s="14"/>
+      <c r="N209" s="14"/>
     </row>
     <row r="210" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="12" t="n">
+      <c r="A210" s="15" t="n">
         <v>41779</v>
       </c>
       <c r="B210" s="9" t="s">
@@ -6959,8 +8025,13 @@
       <c r="G210" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H210" s="17"/>
-      <c r="L210" s="8"/>
+      <c r="H210" s="19"/>
+      <c r="I210" s="12"/>
+      <c r="J210" s="13"/>
+      <c r="K210" s="14"/>
+      <c r="L210" s="14"/>
+      <c r="M210" s="14"/>
+      <c r="N210" s="14"/>
     </row>
     <row r="211" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2" t="s">
@@ -6972,26 +8043,31 @@
       <c r="C211" s="10" t="n">
         <v>0.35</v>
       </c>
-      <c r="D211" s="13" t="n">
+      <c r="D211" s="16" t="n">
         <v>0.385</v>
       </c>
       <c r="E211" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="F211" s="13" t="n">
+      <c r="F211" s="16" t="n">
         <v>0.145</v>
       </c>
       <c r="G211" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H211" s="17"/>
-      <c r="L211" s="8"/>
+      <c r="H211" s="19"/>
+      <c r="I211" s="12"/>
+      <c r="J211" s="13"/>
+      <c r="K211" s="14"/>
+      <c r="L211" s="14"/>
+      <c r="M211" s="14"/>
+      <c r="N211" s="14"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B212" s="18" t="s">
+      <c r="B212" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C212" s="10" t="n">
@@ -7009,8 +8085,13 @@
       <c r="G212" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H212" s="20"/>
-      <c r="L212" s="8"/>
+      <c r="H212" s="22"/>
+      <c r="I212" s="12"/>
+      <c r="J212" s="13"/>
+      <c r="K212" s="14"/>
+      <c r="L212" s="14"/>
+      <c r="M212" s="14"/>
+      <c r="N212" s="14"/>
     </row>
     <row r="213" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2" t="s">
@@ -7034,11 +8115,16 @@
       <c r="G213" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H213" s="17"/>
-      <c r="L213" s="8"/>
+      <c r="H213" s="19"/>
+      <c r="I213" s="12"/>
+      <c r="J213" s="13"/>
+      <c r="K213" s="14"/>
+      <c r="L213" s="14"/>
+      <c r="M213" s="14"/>
+      <c r="N213" s="14"/>
     </row>
     <row r="214" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="12" t="n">
+      <c r="A214" s="15" t="n">
         <v>41763</v>
       </c>
       <c r="B214" s="9" t="s">
@@ -7059,8 +8145,13 @@
       <c r="G214" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H214" s="17"/>
-      <c r="L214" s="8"/>
+      <c r="H214" s="19"/>
+      <c r="I214" s="12"/>
+      <c r="J214" s="13"/>
+      <c r="K214" s="14"/>
+      <c r="L214" s="14"/>
+      <c r="M214" s="14"/>
+      <c r="N214" s="14"/>
     </row>
     <row r="215" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2" t="s">
@@ -7084,11 +8175,16 @@
       <c r="G215" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H215" s="17"/>
-      <c r="L215" s="8"/>
+      <c r="H215" s="19"/>
+      <c r="I215" s="12"/>
+      <c r="J215" s="13"/>
+      <c r="K215" s="14"/>
+      <c r="L215" s="14"/>
+      <c r="M215" s="14"/>
+      <c r="N215" s="14"/>
     </row>
     <row r="216" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="12" t="n">
+      <c r="A216" s="15" t="n">
         <v>41759</v>
       </c>
       <c r="B216" s="9" t="s">
@@ -7109,17 +8205,22 @@
       <c r="G216" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H216" s="17"/>
-      <c r="L216" s="8"/>
+      <c r="H216" s="19"/>
+      <c r="I216" s="12"/>
+      <c r="J216" s="13"/>
+      <c r="K216" s="14"/>
+      <c r="L216" s="14"/>
+      <c r="M216" s="14"/>
+      <c r="N216" s="14"/>
     </row>
     <row r="217" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="12" t="n">
+      <c r="A217" s="15" t="n">
         <v>41751</v>
       </c>
       <c r="B217" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="C217" s="13" t="n">
+      <c r="C217" s="16" t="n">
         <v>0.385</v>
       </c>
       <c r="D217" s="10" t="n">
@@ -7128,17 +8229,22 @@
       <c r="E217" s="10" t="n">
         <v>0.13</v>
       </c>
-      <c r="F217" s="13" t="n">
+      <c r="F217" s="16" t="n">
         <v>0.145</v>
       </c>
       <c r="G217" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H217" s="17"/>
-      <c r="L217" s="8"/>
+      <c r="H217" s="19"/>
+      <c r="I217" s="12"/>
+      <c r="J217" s="13"/>
+      <c r="K217" s="14"/>
+      <c r="L217" s="14"/>
+      <c r="M217" s="14"/>
+      <c r="N217" s="14"/>
     </row>
     <row r="218" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="12" t="n">
+      <c r="A218" s="15" t="n">
         <v>41744</v>
       </c>
       <c r="B218" s="9" t="s">
@@ -7159,11 +8265,16 @@
       <c r="G218" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H218" s="17"/>
-      <c r="L218" s="8"/>
+      <c r="H218" s="19"/>
+      <c r="I218" s="12"/>
+      <c r="J218" s="13"/>
+      <c r="K218" s="14"/>
+      <c r="L218" s="14"/>
+      <c r="M218" s="14"/>
+      <c r="N218" s="14"/>
     </row>
     <row r="219" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="12" t="n">
+      <c r="A219" s="15" t="n">
         <v>41742</v>
       </c>
       <c r="B219" s="9" t="s">
@@ -7184,11 +8295,16 @@
       <c r="G219" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H219" s="17"/>
-      <c r="L219" s="8"/>
+      <c r="H219" s="19"/>
+      <c r="I219" s="12"/>
+      <c r="J219" s="13"/>
+      <c r="K219" s="14"/>
+      <c r="L219" s="14"/>
+      <c r="M219" s="14"/>
+      <c r="N219" s="14"/>
     </row>
     <row r="220" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="12" t="n">
+      <c r="A220" s="15" t="n">
         <v>41737</v>
       </c>
       <c r="B220" s="9" t="s">
@@ -7209,20 +8325,25 @@
       <c r="G220" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H220" s="17"/>
-      <c r="L220" s="8"/>
+      <c r="H220" s="19"/>
+      <c r="I220" s="12"/>
+      <c r="J220" s="13"/>
+      <c r="K220" s="14"/>
+      <c r="L220" s="14"/>
+      <c r="M220" s="14"/>
+      <c r="N220" s="14"/>
     </row>
     <row r="221" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="12" t="n">
+      <c r="A221" s="15" t="n">
         <v>41736</v>
       </c>
       <c r="B221" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="C221" s="13" t="n">
+      <c r="C221" s="16" t="n">
         <v>0.385</v>
       </c>
-      <c r="D221" s="13" t="n">
+      <c r="D221" s="16" t="n">
         <v>0.345</v>
       </c>
       <c r="E221" s="10" t="n">
@@ -7234,8 +8355,13 @@
       <c r="G221" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H221" s="17"/>
-      <c r="L221" s="8"/>
+      <c r="H221" s="19"/>
+      <c r="I221" s="12"/>
+      <c r="J221" s="13"/>
+      <c r="K221" s="14"/>
+      <c r="L221" s="14"/>
+      <c r="M221" s="14"/>
+      <c r="N221" s="14"/>
     </row>
     <row r="222" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2" t="s">
@@ -7259,11 +8385,16 @@
       <c r="G222" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H222" s="20"/>
-      <c r="L222" s="8"/>
+      <c r="H222" s="22"/>
+      <c r="I222" s="12"/>
+      <c r="J222" s="13"/>
+      <c r="K222" s="14"/>
+      <c r="L222" s="14"/>
+      <c r="M222" s="14"/>
+      <c r="N222" s="14"/>
     </row>
     <row r="223" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="12" t="n">
+      <c r="A223" s="15" t="n">
         <v>41723</v>
       </c>
       <c r="B223" s="9" t="s">
@@ -7272,23 +8403,28 @@
       <c r="C223" s="10" t="n">
         <v>0.38</v>
       </c>
-      <c r="D223" s="13" t="n">
+      <c r="D223" s="16" t="n">
         <v>0.385</v>
       </c>
       <c r="E223" s="10" t="n">
         <v>0.11</v>
       </c>
-      <c r="F223" s="13" t="n">
+      <c r="F223" s="16" t="n">
         <v>0.125</v>
       </c>
       <c r="G223" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H223" s="16"/>
-      <c r="L223" s="8"/>
+      <c r="H223" s="18"/>
+      <c r="I223" s="12"/>
+      <c r="J223" s="13"/>
+      <c r="K223" s="14"/>
+      <c r="L223" s="14"/>
+      <c r="M223" s="14"/>
+      <c r="N223" s="14"/>
     </row>
     <row r="224" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="12" t="n">
+      <c r="A224" s="15" t="n">
         <v>41723</v>
       </c>
       <c r="B224" s="9" t="s">
@@ -7309,8 +8445,13 @@
       <c r="G224" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H224" s="20"/>
-      <c r="L224" s="8"/>
+      <c r="H224" s="22"/>
+      <c r="I224" s="12"/>
+      <c r="J224" s="13"/>
+      <c r="K224" s="14"/>
+      <c r="L224" s="14"/>
+      <c r="M224" s="14"/>
+      <c r="N224" s="14"/>
     </row>
     <row r="225" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2" t="s">
@@ -7334,11 +8475,16 @@
       <c r="G225" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H225" s="16"/>
-      <c r="L225" s="8"/>
+      <c r="H225" s="18"/>
+      <c r="I225" s="12"/>
+      <c r="J225" s="13"/>
+      <c r="K225" s="14"/>
+      <c r="L225" s="14"/>
+      <c r="M225" s="14"/>
+      <c r="N225" s="14"/>
     </row>
     <row r="226" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="12" t="n">
+      <c r="A226" s="15" t="n">
         <v>41716</v>
       </c>
       <c r="B226" s="9" t="s">
@@ -7359,8 +8505,13 @@
       <c r="G226" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H226" s="17"/>
-      <c r="L226" s="8"/>
+      <c r="H226" s="19"/>
+      <c r="I226" s="12"/>
+      <c r="J226" s="13"/>
+      <c r="K226" s="14"/>
+      <c r="L226" s="14"/>
+      <c r="M226" s="14"/>
+      <c r="N226" s="14"/>
     </row>
     <row r="227" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2" t="s">
@@ -7384,14 +8535,19 @@
       <c r="G227" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H227" s="16"/>
-      <c r="L227" s="8"/>
+      <c r="H227" s="18"/>
+      <c r="I227" s="12"/>
+      <c r="J227" s="13"/>
+      <c r="K227" s="14"/>
+      <c r="L227" s="14"/>
+      <c r="M227" s="14"/>
+      <c r="N227" s="14"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B228" s="18" t="s">
+      <c r="B228" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C228" s="10" t="n">
@@ -7409,11 +8565,16 @@
       <c r="G228" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H228" s="16"/>
-      <c r="L228" s="8"/>
+      <c r="H228" s="18"/>
+      <c r="I228" s="12"/>
+      <c r="J228" s="13"/>
+      <c r="K228" s="14"/>
+      <c r="L228" s="14"/>
+      <c r="M228" s="14"/>
+      <c r="N228" s="14"/>
     </row>
     <row r="229" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="12" t="n">
+      <c r="A229" s="15" t="n">
         <v>41703</v>
       </c>
       <c r="B229" s="9" t="s">
@@ -7434,11 +8595,16 @@
       <c r="G229" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H229" s="17"/>
-      <c r="L229" s="8"/>
+      <c r="H229" s="19"/>
+      <c r="I229" s="12"/>
+      <c r="J229" s="13"/>
+      <c r="K229" s="14"/>
+      <c r="L229" s="14"/>
+      <c r="M229" s="14"/>
+      <c r="N229" s="14"/>
     </row>
     <row r="230" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="12" t="n">
+      <c r="A230" s="15" t="n">
         <v>41693</v>
       </c>
       <c r="B230" s="9" t="s">
@@ -7447,10 +8613,10 @@
       <c r="C230" s="10" t="n">
         <v>0.41</v>
       </c>
-      <c r="D230" s="13" t="n">
+      <c r="D230" s="16" t="n">
         <v>0.355</v>
       </c>
-      <c r="E230" s="13" t="n">
+      <c r="E230" s="16" t="n">
         <v>0.105</v>
       </c>
       <c r="F230" s="10" t="n">
@@ -7459,8 +8625,13 @@
       <c r="G230" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H230" s="16"/>
-      <c r="L230" s="8"/>
+      <c r="H230" s="18"/>
+      <c r="I230" s="12"/>
+      <c r="J230" s="13"/>
+      <c r="K230" s="14"/>
+      <c r="L230" s="14"/>
+      <c r="M230" s="14"/>
+      <c r="N230" s="14"/>
     </row>
     <row r="231" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2" t="s">
@@ -7484,11 +8655,16 @@
       <c r="G231" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H231" s="20"/>
-      <c r="L231" s="8"/>
+      <c r="H231" s="22"/>
+      <c r="I231" s="12"/>
+      <c r="J231" s="13"/>
+      <c r="K231" s="14"/>
+      <c r="L231" s="14"/>
+      <c r="M231" s="14"/>
+      <c r="N231" s="14"/>
     </row>
     <row r="232" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="12" t="n">
+      <c r="A232" s="15" t="n">
         <v>41685</v>
       </c>
       <c r="B232" s="9" t="s">
@@ -7509,8 +8685,13 @@
       <c r="G232" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H232" s="17"/>
-      <c r="L232" s="8"/>
+      <c r="H232" s="19"/>
+      <c r="I232" s="12"/>
+      <c r="J232" s="13"/>
+      <c r="K232" s="14"/>
+      <c r="L232" s="14"/>
+      <c r="M232" s="14"/>
+      <c r="N232" s="14"/>
     </row>
     <row r="233" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="2" t="s">
@@ -7534,23 +8715,28 @@
       <c r="G233" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H233" s="16"/>
-      <c r="L233" s="8"/>
+      <c r="H233" s="18"/>
+      <c r="I233" s="12"/>
+      <c r="J233" s="13"/>
+      <c r="K233" s="14"/>
+      <c r="L233" s="14"/>
+      <c r="M233" s="14"/>
+      <c r="N233" s="14"/>
     </row>
     <row r="234" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="12" t="n">
+      <c r="A234" s="15" t="n">
         <v>41667</v>
       </c>
       <c r="B234" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="C234" s="13" t="n">
+      <c r="C234" s="16" t="n">
         <v>0.395</v>
       </c>
       <c r="D234" s="10" t="n">
         <v>0.37</v>
       </c>
-      <c r="E234" s="13" t="n">
+      <c r="E234" s="16" t="n">
         <v>0.115</v>
       </c>
       <c r="F234" s="10" t="n">
@@ -7559,33 +8745,43 @@
       <c r="G234" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H234" s="17"/>
-      <c r="L234" s="8"/>
+      <c r="H234" s="19"/>
+      <c r="I234" s="12"/>
+      <c r="J234" s="13"/>
+      <c r="K234" s="14"/>
+      <c r="L234" s="14"/>
+      <c r="M234" s="14"/>
+      <c r="N234" s="14"/>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="12" t="n">
+      <c r="A235" s="15" t="n">
         <v>41662</v>
       </c>
-      <c r="B235" s="18" t="s">
+      <c r="B235" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="C235" s="13" t="n">
+      <c r="C235" s="16" t="n">
         <v>0.398</v>
       </c>
-      <c r="D235" s="13" t="n">
+      <c r="D235" s="16" t="n">
         <v>0.406</v>
       </c>
-      <c r="E235" s="13" t="n">
+      <c r="E235" s="16" t="n">
         <v>0.091</v>
       </c>
-      <c r="F235" s="13" t="n">
+      <c r="F235" s="16" t="n">
         <v>0.091</v>
       </c>
       <c r="G235" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H235" s="17"/>
-      <c r="L235" s="8"/>
+      <c r="H235" s="19"/>
+      <c r="I235" s="12"/>
+      <c r="J235" s="13"/>
+      <c r="K235" s="14"/>
+      <c r="L235" s="14"/>
+      <c r="M235" s="14"/>
+      <c r="N235" s="14"/>
     </row>
     <row r="236" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="2" t="s">
@@ -7609,11 +8805,16 @@
       <c r="G236" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H236" s="17"/>
-      <c r="L236" s="8"/>
+      <c r="H236" s="19"/>
+      <c r="I236" s="12"/>
+      <c r="J236" s="13"/>
+      <c r="K236" s="14"/>
+      <c r="L236" s="14"/>
+      <c r="M236" s="14"/>
+      <c r="N236" s="14"/>
     </row>
     <row r="237" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="12" t="n">
+      <c r="A237" s="15" t="n">
         <v>41652</v>
       </c>
       <c r="B237" s="9" t="s">
@@ -7625,29 +8826,34 @@
       <c r="D237" s="10" t="n">
         <v>0.39</v>
       </c>
-      <c r="E237" s="13" t="n">
+      <c r="E237" s="16" t="n">
         <v>0.105</v>
       </c>
-      <c r="F237" s="13" t="n">
+      <c r="F237" s="16" t="n">
         <v>0.125</v>
       </c>
       <c r="G237" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H237" s="16"/>
-      <c r="L237" s="8"/>
+      <c r="H237" s="18"/>
+      <c r="I237" s="12"/>
+      <c r="J237" s="13"/>
+      <c r="K237" s="14"/>
+      <c r="L237" s="14"/>
+      <c r="M237" s="14"/>
+      <c r="N237" s="14"/>
     </row>
     <row r="238" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="12" t="n">
+      <c r="A238" s="15" t="n">
         <v>41624</v>
       </c>
       <c r="B238" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="C238" s="13" t="n">
+      <c r="C238" s="16" t="n">
         <v>0.405</v>
       </c>
-      <c r="D238" s="13" t="n">
+      <c r="D238" s="16" t="n">
         <v>0.385</v>
       </c>
       <c r="E238" s="10" t="n">
@@ -7659,39 +8865,49 @@
       <c r="G238" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H238" s="20"/>
-      <c r="L238" s="8"/>
+      <c r="H238" s="22"/>
+      <c r="I238" s="12"/>
+      <c r="J238" s="13"/>
+      <c r="K238" s="14"/>
+      <c r="L238" s="14"/>
+      <c r="M238" s="14"/>
+      <c r="N238" s="14"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="12" t="n">
+      <c r="A239" s="15" t="n">
         <v>41623</v>
       </c>
-      <c r="B239" s="18" t="s">
+      <c r="B239" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="C239" s="13" t="n">
+      <c r="C239" s="16" t="n">
         <v>0.414</v>
       </c>
-      <c r="D239" s="13" t="n">
+      <c r="D239" s="16" t="n">
         <v>0.404</v>
       </c>
-      <c r="E239" s="13" t="n">
+      <c r="E239" s="16" t="n">
         <v>0.087</v>
       </c>
-      <c r="F239" s="13" t="n">
+      <c r="F239" s="16" t="n">
         <v>0.095</v>
       </c>
       <c r="G239" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H239" s="20"/>
-      <c r="L239" s="8"/>
+      <c r="H239" s="22"/>
+      <c r="I239" s="12"/>
+      <c r="J239" s="13"/>
+      <c r="K239" s="14"/>
+      <c r="L239" s="14"/>
+      <c r="M239" s="14"/>
+      <c r="N239" s="14"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B240" s="18" t="s">
+      <c r="B240" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C240" s="10" t="n">
@@ -7709,8 +8925,13 @@
       <c r="G240" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H240" s="17"/>
-      <c r="L240" s="8"/>
+      <c r="H240" s="19"/>
+      <c r="I240" s="12"/>
+      <c r="J240" s="13"/>
+      <c r="K240" s="14"/>
+      <c r="L240" s="14"/>
+      <c r="M240" s="14"/>
+      <c r="N240" s="14"/>
     </row>
     <row r="241" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="2" t="s">
@@ -7734,8 +8955,13 @@
       <c r="G241" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H241" s="17"/>
-      <c r="L241" s="8"/>
+      <c r="H241" s="19"/>
+      <c r="I241" s="12"/>
+      <c r="J241" s="13"/>
+      <c r="K241" s="14"/>
+      <c r="L241" s="14"/>
+      <c r="M241" s="14"/>
+      <c r="N241" s="14"/>
     </row>
     <row r="242" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2" t="s">
@@ -7744,29 +8970,34 @@
       <c r="B242" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="C242" s="13" t="n">
+      <c r="C242" s="16" t="n">
         <v>0.415</v>
       </c>
-      <c r="D242" s="13" t="n">
+      <c r="D242" s="16" t="n">
         <v>0.385</v>
       </c>
-      <c r="E242" s="13" t="n">
+      <c r="E242" s="16" t="n">
         <v>0.085</v>
       </c>
-      <c r="F242" s="13" t="n">
+      <c r="F242" s="16" t="n">
         <v>0.125</v>
       </c>
       <c r="G242" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H242" s="16"/>
-      <c r="L242" s="8"/>
+      <c r="H242" s="18"/>
+      <c r="I242" s="12"/>
+      <c r="J242" s="13"/>
+      <c r="K242" s="14"/>
+      <c r="L242" s="14"/>
+      <c r="M242" s="14"/>
+      <c r="N242" s="14"/>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B243" s="18" t="s">
+      <c r="B243" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C243" s="10" t="n">
@@ -7784,8 +9015,13 @@
       <c r="G243" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H243" s="20"/>
-      <c r="L243" s="8"/>
+      <c r="H243" s="22"/>
+      <c r="I243" s="12"/>
+      <c r="J243" s="13"/>
+      <c r="K243" s="14"/>
+      <c r="L243" s="14"/>
+      <c r="M243" s="14"/>
+      <c r="N243" s="14"/>
     </row>
     <row r="244" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2" t="s">
@@ -7809,14 +9045,19 @@
       <c r="G244" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H244" s="16"/>
-      <c r="L244" s="8"/>
+      <c r="H244" s="18"/>
+      <c r="I244" s="12"/>
+      <c r="J244" s="13"/>
+      <c r="K244" s="14"/>
+      <c r="L244" s="14"/>
+      <c r="M244" s="14"/>
+      <c r="N244" s="14"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="B245" s="18" t="s">
+      <c r="B245" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C245" s="10" t="n">
@@ -7834,14 +9075,19 @@
       <c r="G245" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H245" s="17"/>
-      <c r="L245" s="8"/>
+      <c r="H245" s="19"/>
+      <c r="I245" s="12"/>
+      <c r="J245" s="13"/>
+      <c r="K245" s="14"/>
+      <c r="L245" s="14"/>
+      <c r="M245" s="14"/>
+      <c r="N245" s="14"/>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="B246" s="18" t="s">
+      <c r="B246" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C246" s="10" t="n">
@@ -7859,8 +9105,13 @@
       <c r="G246" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H246" s="16"/>
-      <c r="L246" s="8"/>
+      <c r="H246" s="18"/>
+      <c r="I246" s="12"/>
+      <c r="J246" s="13"/>
+      <c r="K246" s="14"/>
+      <c r="L246" s="14"/>
+      <c r="M246" s="14"/>
+      <c r="N246" s="14"/>
     </row>
     <row r="247" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="2" t="s">
@@ -7869,10 +9120,10 @@
       <c r="B247" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="C247" s="13" t="n">
+      <c r="C247" s="16" t="n">
         <v>0.435</v>
       </c>
-      <c r="D247" s="13" t="n">
+      <c r="D247" s="16" t="n">
         <v>0.345</v>
       </c>
       <c r="E247" s="10" t="n">
@@ -7884,8 +9135,13 @@
       <c r="G247" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H247" s="16"/>
-      <c r="L247" s="8"/>
+      <c r="H247" s="18"/>
+      <c r="I247" s="12"/>
+      <c r="J247" s="13"/>
+      <c r="K247" s="14"/>
+      <c r="L247" s="14"/>
+      <c r="M247" s="14"/>
+      <c r="N247" s="14"/>
     </row>
     <row r="248" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2" t="s">
@@ -7894,13 +9150,13 @@
       <c r="B248" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="C248" s="13" t="n">
+      <c r="C248" s="16" t="n">
         <v>0.435</v>
       </c>
       <c r="D248" s="10" t="n">
         <v>0.34</v>
       </c>
-      <c r="E248" s="13" t="n">
+      <c r="E248" s="16" t="n">
         <v>0.105</v>
       </c>
       <c r="F248" s="10" t="n">
@@ -7909,8 +9165,13 @@
       <c r="G248" s="8" t="n">
         <v>1500</v>
       </c>
-      <c r="H248" s="14"/>
-      <c r="L248" s="8"/>
+      <c r="H248" s="17"/>
+      <c r="I248" s="12"/>
+      <c r="J248" s="13"/>
+      <c r="K248" s="14"/>
+      <c r="L248" s="14"/>
+      <c r="M248" s="14"/>
+      <c r="N248" s="14"/>
     </row>
     <row r="249" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="2" t="s">
@@ -7934,8 +9195,13 @@
       <c r="G249" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H249" s="14"/>
-      <c r="L249" s="8"/>
+      <c r="H249" s="17"/>
+      <c r="I249" s="12"/>
+      <c r="J249" s="13"/>
+      <c r="K249" s="14"/>
+      <c r="L249" s="14"/>
+      <c r="M249" s="14"/>
+      <c r="N249" s="14"/>
     </row>
     <row r="250" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="2" t="s">
@@ -7959,83 +9225,112 @@
       <c r="G250" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="H250" s="16"/>
-      <c r="L250" s="8"/>
+      <c r="H250" s="18"/>
+      <c r="I250" s="12"/>
+      <c r="J250" s="13"/>
+      <c r="K250" s="14"/>
+      <c r="L250" s="14"/>
+      <c r="M250" s="14"/>
+      <c r="N250" s="14"/>
     </row>
     <row r="251" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="25" t="n">
+      <c r="A251" s="28" t="n">
         <v>41524</v>
       </c>
-      <c r="B251" s="26" t="s">
+      <c r="B251" s="29" t="s">
         <v>332</v>
       </c>
-      <c r="C251" s="27" t="n">
+      <c r="C251" s="30" t="n">
         <v>0.456</v>
       </c>
-      <c r="D251" s="27" t="n">
+      <c r="D251" s="30" t="n">
         <v>0.334</v>
       </c>
-      <c r="E251" s="27" t="n">
+      <c r="E251" s="30" t="n">
         <v>0.087</v>
       </c>
-      <c r="F251" s="27" t="n">
+      <c r="F251" s="30" t="n">
         <v>0.123</v>
       </c>
       <c r="G251" s="8"/>
-      <c r="H251" s="16"/>
-      <c r="L251" s="8"/>
+      <c r="H251" s="18"/>
+      <c r="I251" s="12"/>
+      <c r="J251" s="12"/>
+      <c r="K251" s="14"/>
+      <c r="L251" s="14"/>
+      <c r="M251" s="14"/>
+      <c r="N251" s="14"/>
+      <c r="O251" s="31"/>
+      <c r="P251" s="14"/>
+      <c r="Q251" s="8"/>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B252" s="18" t="s">
+      <c r="B252" s="20" t="s">
         <v>334</v>
       </c>
       <c r="C252" s="10" t="n">
         <v>0.45</v>
       </c>
-      <c r="D252" s="13" t="n">
+      <c r="D252" s="16" t="n">
         <v>0.315</v>
       </c>
-      <c r="E252" s="13" t="n">
+      <c r="E252" s="16" t="n">
         <v>0.095</v>
       </c>
       <c r="F252" s="10" t="n">
         <v>0.14</v>
       </c>
       <c r="G252" s="8"/>
-      <c r="H252" s="14"/>
-      <c r="L252" s="8"/>
+      <c r="H252" s="17"/>
+      <c r="I252" s="12"/>
+      <c r="J252" s="13"/>
+      <c r="K252" s="14"/>
+      <c r="L252" s="14"/>
+      <c r="M252" s="14"/>
+      <c r="N252" s="14"/>
+      <c r="O252" s="31"/>
+      <c r="P252" s="14"/>
+      <c r="Q252" s="8"/>
     </row>
     <row r="253" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="12" t="n">
+      <c r="A253" s="15" t="n">
         <v>41522</v>
       </c>
       <c r="B253" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="C253" s="13" t="n">
+      <c r="C253" s="16" t="n">
         <v>0.435</v>
       </c>
-      <c r="D253" s="13" t="n">
+      <c r="D253" s="16" t="n">
         <v>0.337</v>
       </c>
-      <c r="E253" s="13" t="n">
+      <c r="E253" s="16" t="n">
         <v>0.102</v>
       </c>
-      <c r="F253" s="13" t="n">
+      <c r="F253" s="16" t="n">
         <v>0.126</v>
       </c>
       <c r="G253" s="8"/>
-      <c r="H253" s="14"/>
-      <c r="L253" s="8"/>
+      <c r="H253" s="17"/>
+      <c r="I253" s="12"/>
+      <c r="J253" s="13"/>
+      <c r="K253" s="14"/>
+      <c r="L253" s="14"/>
+      <c r="M253" s="14"/>
+      <c r="N253" s="14"/>
+      <c r="O253" s="31"/>
+      <c r="P253" s="14"/>
+      <c r="Q253" s="8"/>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B254" s="18" t="s">
+      <c r="B254" s="20" t="s">
         <v>246</v>
       </c>
       <c r="C254" s="10" t="n">
@@ -8051,20 +9346,26 @@
         <v>0.12</v>
       </c>
       <c r="G254" s="8"/>
-      <c r="H254" s="16"/>
-      <c r="L254" s="8"/>
+      <c r="H254" s="18"/>
+      <c r="I254" s="12"/>
+      <c r="J254" s="13"/>
+      <c r="K254" s="14"/>
+      <c r="L254" s="14"/>
+      <c r="M254" s="14"/>
+      <c r="N254" s="14"/>
+      <c r="O254" s="31"/>
+      <c r="P254" s="14"/>
+      <c r="Q254" s="8"/>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G255" s="8"/>
-      <c r="H255" s="16"/>
-      <c r="L255" s="8"/>
+      <c r="H255" s="18"/>
+      <c r="I255" s="12"/>
+      <c r="Q255" s="8"/>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G256" s="8"/>
-      <c r="L256" s="8"/>
-    </row>
-    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L257" s="8"/>
+      <c r="Q256" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
